--- a/premise/data/additional_inventories/lci-ships.xlsx
+++ b/premise/data/additional_inventories/lci-ships.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF4F689-4E17-1741-A45E-48F2FB1E57CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79BDFBC-15F6-A849-92C7-44ACDC21BD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20240" yWindow="720" windowWidth="22420" windowHeight="23000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inventories" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="200">
   <si>
     <t>Database</t>
   </si>
@@ -627,6 +627,15 @@
   </si>
   <si>
     <t>80% reduction relative to using HFO at 75% engine load, according to Petzold et al., 2011, dx.doi.org/10.1021/es2021439</t>
+  </si>
+  <si>
+    <t>LPG (propane and butane)</t>
+  </si>
+  <si>
+    <t>26--27</t>
+  </si>
+  <si>
+    <t>9% penalty of load carrying capacity, due to the low gravimetric density of LPG.</t>
   </si>
 </sst>
 </file>
@@ -634,11 +643,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -701,7 +710,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
@@ -709,12 +718,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -723,17 +732,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3759,8 +3768,8 @@
         <v>93</v>
       </c>
       <c r="B156" s="11">
-        <f>parameters!N9</f>
-        <v>158400000000</v>
+        <f>parameters!N11</f>
+        <v>163923092656.98508</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
@@ -3768,8 +3777,8 @@
         <v>94</v>
       </c>
       <c r="B157" s="11">
-        <f>parameters!O9</f>
-        <v>153000000000</v>
+        <f>parameters!O11</f>
+        <v>159903865821.23132</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
@@ -3777,8 +3786,8 @@
         <v>95</v>
       </c>
       <c r="B158" s="11">
-        <f>parameters!P9</f>
-        <v>162000000000</v>
+        <f>parameters!P11</f>
+        <v>166602577214.15421</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
@@ -3786,8 +3795,8 @@
         <v>156</v>
       </c>
       <c r="B159" s="13">
-        <f>parameters!I9</f>
-        <v>0.12</v>
+        <f>parameters!I11</f>
+        <v>8.9316151905638519E-2</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
@@ -3795,8 +3804,8 @@
         <v>157</v>
       </c>
       <c r="B160" s="13">
-        <f>parameters!J9</f>
-        <v>0.1</v>
+        <f>parameters!J11</f>
+        <v>7.4430126588032122E-2</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
@@ -3804,8 +3813,8 @@
         <v>158</v>
       </c>
       <c r="B161" s="13">
-        <f>parameters!K9</f>
-        <v>0.15</v>
+        <f>parameters!K11</f>
+        <v>0.11164518988204816</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.2">
@@ -3822,7 +3831,7 @@
         <v>131</v>
       </c>
       <c r="B163" s="13">
-        <f>parameters!C20</f>
+        <f>parameters!C23</f>
         <v>0.49342105263157898</v>
       </c>
     </row>
@@ -3831,7 +3840,7 @@
         <v>132</v>
       </c>
       <c r="B164" s="13">
-        <f>parameters!D20</f>
+        <f>parameters!D23</f>
         <v>0.44407894736842107</v>
       </c>
     </row>
@@ -3840,7 +3849,7 @@
         <v>133</v>
       </c>
       <c r="B165" s="13">
-        <f>parameters!E20</f>
+        <f>parameters!E23</f>
         <v>0.54276315789473695</v>
       </c>
     </row>
@@ -3916,7 +3925,7 @@
       </c>
       <c r="B169" s="12">
         <f>0.11*(B162/B163)/46/(1-B159)</f>
-        <v>2.3405797101449274E-3</v>
+        <v>2.261718102541901E-3</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
@@ -3938,15 +3947,15 @@
       </c>
       <c r="J169">
         <f>B169</f>
-        <v>2.3405797101449274E-3</v>
+        <v>2.261718102541901E-3</v>
       </c>
       <c r="K169" s="6">
         <f>0.11*(B162/B165)/46/(1-B160)</f>
-        <v>2.080515297906602E-3</v>
+        <v>2.0230388022607075E-3</v>
       </c>
       <c r="L169" s="6">
         <f>0.11*(B162/B164)/46/(1-B161)</f>
-        <v>2.6924315619967797E-3</v>
+        <v>2.5761855529249592E-3</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.2">
@@ -3955,7 +3964,7 @@
       </c>
       <c r="B170" s="11">
         <f>1/B156</f>
-        <v>6.313131313131313E-12</v>
+        <v>6.1004217513912804E-12</v>
       </c>
       <c r="C170" t="s">
         <v>19</v>
@@ -3970,22 +3979,22 @@
         <v>43</v>
       </c>
       <c r="H170" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="I170">
         <v>5</v>
       </c>
       <c r="J170" s="11">
         <f>B170</f>
-        <v>6.313131313131313E-12</v>
+        <v>6.1004217513912804E-12</v>
       </c>
       <c r="K170" s="11">
         <f>1/B158</f>
-        <v>6.1728395061728393E-12</v>
+        <v>6.0023081078426567E-12</v>
       </c>
       <c r="L170" s="11">
         <f>1/B157</f>
-        <v>6.5359477124183003E-12</v>
+        <v>6.25375749900866E-12</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
@@ -3994,7 +4003,7 @@
       </c>
       <c r="B171" s="11">
         <f>1/B156</f>
-        <v>6.313131313131313E-12</v>
+        <v>6.1004217513912804E-12</v>
       </c>
       <c r="C171" t="s">
         <v>19</v>
@@ -4009,22 +4018,22 @@
         <v>49</v>
       </c>
       <c r="H171" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="I171">
         <v>5</v>
       </c>
       <c r="J171" s="11">
         <f>B171</f>
-        <v>6.313131313131313E-12</v>
+        <v>6.1004217513912804E-12</v>
       </c>
       <c r="K171" s="11">
         <f>1/B158</f>
-        <v>6.1728395061728393E-12</v>
+        <v>6.0023081078426567E-12</v>
       </c>
       <c r="L171" s="11">
         <f>1/B157</f>
-        <v>6.5359477124183003E-12</v>
+        <v>6.25375749900866E-12</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.2">
@@ -4057,7 +4066,7 @@
       </c>
       <c r="B173" s="12">
         <f>B169*3</f>
-        <v>7.0217391304347818E-3</v>
+        <v>6.7851543076257025E-3</v>
       </c>
       <c r="D173" t="s">
         <v>23</v>
@@ -4076,15 +4085,15 @@
       </c>
       <c r="J173" s="6">
         <f>B173</f>
-        <v>7.0217391304347818E-3</v>
+        <v>6.7851543076257025E-3</v>
       </c>
       <c r="K173" s="6">
         <f>K169*3</f>
-        <v>6.2415458937198059E-3</v>
+        <v>6.069116406782123E-3</v>
       </c>
       <c r="L173" s="6">
         <f>L169*3</f>
-        <v>8.0772946859903397E-3</v>
+        <v>7.7285566587748777E-3</v>
       </c>
     </row>
     <row r="174" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -4093,7 +4102,7 @@
       </c>
       <c r="B174" s="11">
         <f>0.00186*(B169*46*B163/3.6)</f>
-        <v>2.7447916666666669E-5</v>
+        <v>2.6523108669611446E-5</v>
       </c>
       <c r="D174" t="s">
         <v>23</v>
@@ -4112,15 +4121,15 @@
       </c>
       <c r="J174" s="6">
         <f t="shared" ref="J174:J180" si="6">B174</f>
-        <v>2.7447916666666669E-5</v>
+        <v>2.6523108669611446E-5</v>
       </c>
       <c r="K174" s="6">
         <f>0.00186*(B169*46*B164/3.6)</f>
-        <v>2.4703125000000002E-5</v>
+        <v>2.3870797802650298E-5</v>
       </c>
       <c r="L174" s="6">
         <f>0.00186*(B169*46*B165/3.6)</f>
-        <v>3.0192708333333338E-5</v>
+        <v>2.9175419536572591E-5</v>
       </c>
     </row>
     <row r="175" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -4129,7 +4138,7 @@
       </c>
       <c r="B175">
         <f>0.00117*(B169*46*B163/3.6)</f>
-        <v>1.7265625000000001E-5</v>
+        <v>1.6683890937336232E-5</v>
       </c>
       <c r="D175" t="s">
         <v>23</v>
@@ -4148,15 +4157,15 @@
       </c>
       <c r="J175" s="6">
         <f t="shared" si="6"/>
-        <v>1.7265625000000001E-5</v>
+        <v>1.6683890937336232E-5</v>
       </c>
       <c r="K175" s="6">
         <f>0.00117*(B169*46*B164/3.6)</f>
-        <v>1.5539062499999999E-5</v>
+        <v>1.5015501843602608E-5</v>
       </c>
       <c r="L175" s="6">
         <f>0.00117*(B169*46*B165/3.6)</f>
-        <v>1.8992187500000003E-5</v>
+        <v>1.8352280031069855E-5</v>
       </c>
     </row>
     <row r="176" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -4165,7 +4174,7 @@
       </c>
       <c r="B176" s="11">
         <f>0.00003*(B169*46*B163/3.6)</f>
-        <v>4.4270833333333331E-7</v>
+        <v>4.2779207531631361E-7</v>
       </c>
       <c r="D176" t="s">
         <v>23</v>
@@ -4184,15 +4193,15 @@
       </c>
       <c r="J176" s="6">
         <f t="shared" si="6"/>
-        <v>4.4270833333333331E-7</v>
+        <v>4.2779207531631361E-7</v>
       </c>
       <c r="K176" s="6">
         <f>0.00003*(B169*46*B164/3.6)</f>
-        <v>3.984375E-7</v>
+        <v>3.8501286778468222E-7</v>
       </c>
       <c r="L176" s="6">
         <f>0.00003*(B169*46*B165/3.6)</f>
-        <v>4.8697916666666668E-7</v>
+        <v>4.7057128284794499E-7</v>
       </c>
     </row>
     <row r="177" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -4201,7 +4210,7 @@
       </c>
       <c r="B177" s="11">
         <f>0.00003*(B169*46*B163/3.6)</f>
-        <v>4.4270833333333331E-7</v>
+        <v>4.2779207531631361E-7</v>
       </c>
       <c r="D177" t="s">
         <v>23</v>
@@ -4220,15 +4229,15 @@
       </c>
       <c r="J177" s="6">
         <f t="shared" si="6"/>
-        <v>4.4270833333333331E-7</v>
+        <v>4.2779207531631361E-7</v>
       </c>
       <c r="K177" s="6">
         <f>0.00003*(B169*46*B164/3.6)</f>
-        <v>3.984375E-7</v>
+        <v>3.8501286778468222E-7</v>
       </c>
       <c r="L177" s="6">
         <f>0.00003*(B169*46*B165/3.6)</f>
-        <v>4.8697916666666668E-7</v>
+        <v>4.7057128284794499E-7</v>
       </c>
     </row>
     <row r="178" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -4237,7 +4246,7 @@
       </c>
       <c r="B178" s="11">
         <f>B169*0.02</f>
-        <v>4.6811594202898551E-5</v>
+        <v>4.5234362050838021E-5</v>
       </c>
       <c r="D178" t="s">
         <v>23</v>
@@ -4256,15 +4265,15 @@
       </c>
       <c r="J178" s="6">
         <f t="shared" si="6"/>
-        <v>4.6811594202898551E-5</v>
+        <v>4.5234362050838021E-5</v>
       </c>
       <c r="K178" s="6">
         <f>J178</f>
-        <v>4.6811594202898551E-5</v>
+        <v>4.5234362050838021E-5</v>
       </c>
       <c r="L178" s="6">
         <f>0.067*B169</f>
-        <v>1.5681884057971014E-4</v>
+        <v>1.5153511287030737E-4</v>
       </c>
     </row>
     <row r="179" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -4273,7 +4282,7 @@
       </c>
       <c r="B179" s="11">
         <f>0.00038*(B169*46*B163/3.6)</f>
-        <v>5.607638888888889E-6</v>
+        <v>5.4186996206733058E-6</v>
       </c>
       <c r="D179" t="s">
         <v>23</v>
@@ -4292,15 +4301,15 @@
       </c>
       <c r="J179" s="6">
         <f t="shared" si="6"/>
-        <v>5.607638888888889E-6</v>
+        <v>5.4186996206733058E-6</v>
       </c>
       <c r="K179" s="6">
         <f>0.00038*(B169*46*B164/3.6)</f>
-        <v>5.0468749999999999E-6</v>
+        <v>4.8768296586059753E-6</v>
       </c>
       <c r="L179" s="6">
         <f>0.00038*(B169*46*B165/3.6)</f>
-        <v>6.168402777777779E-6</v>
+        <v>5.9605695827406364E-6</v>
       </c>
     </row>
     <row r="180" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -4309,7 +4318,7 @@
       </c>
       <c r="B180" s="11">
         <f>0.00002*(B169*46*B163/3.6)</f>
-        <v>2.9513888888888889E-7</v>
+        <v>2.8519471687754242E-7</v>
       </c>
       <c r="D180" t="s">
         <v>23</v>
@@ -4328,15 +4337,15 @@
       </c>
       <c r="J180" s="6">
         <f t="shared" si="6"/>
-        <v>2.9513888888888889E-7</v>
+        <v>2.8519471687754242E-7</v>
       </c>
       <c r="K180" s="11">
         <f>0.00002*(B169*46*B164/3.6)</f>
-        <v>2.65625E-7</v>
+        <v>2.5667524518978816E-7</v>
       </c>
       <c r="L180">
         <f>0.00002*(B169*46*B165/3.6)</f>
-        <v>3.2465277777777784E-7</v>
+        <v>3.1371418856529668E-7</v>
       </c>
     </row>
     <row r="182" spans="1:12" ht="16" x14ac:dyDescent="0.2">
@@ -6064,7 +6073,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F1A7F4-A2B5-7747-AA61-2990069064F9}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" bestFit="1" customWidth="1"/>
@@ -6195,14 +6204,14 @@
         <v>0.43880000000000002</v>
       </c>
       <c r="E5" s="16">
-        <f t="shared" ref="E5:E10" si="0">1/D5</f>
+        <f t="shared" ref="E5:E11" si="0">1/D5</f>
         <v>2.2789425706472195</v>
       </c>
       <c r="F5" s="16">
         <v>1.1000000000000001</v>
       </c>
       <c r="G5" s="16">
-        <f t="shared" ref="G5:G10" si="1">E5*F5</f>
+        <f t="shared" ref="G5:G11" si="1">E5*F5</f>
         <v>2.5068368277119415</v>
       </c>
       <c r="H5" s="14">
@@ -6422,7 +6431,7 @@
         <v>1.8000327278677795</v>
       </c>
       <c r="H9" s="14">
-        <f t="shared" si="2"/>
+        <f>1-(1/G9)</f>
         <v>0.44445454545454544</v>
       </c>
       <c r="I9" s="13">
@@ -6506,6 +6515,63 @@
         <v>117000000000</v>
       </c>
     </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="16">
+        <f>26.5/36</f>
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="E11" s="16">
+        <f t="shared" si="0"/>
+        <v>1.3584905660377358</v>
+      </c>
+      <c r="F11" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G11" s="16">
+        <f t="shared" si="1"/>
+        <v>1.4943396226415095</v>
+      </c>
+      <c r="H11" s="14">
+        <f>1-(1/G11)</f>
+        <v>0.33080808080808088</v>
+      </c>
+      <c r="I11" s="13">
+        <f>I9*H11/H9</f>
+        <v>8.9316151905638519E-2</v>
+      </c>
+      <c r="J11" s="13">
+        <f>J9*H11/H9</f>
+        <v>7.4430126588032122E-2</v>
+      </c>
+      <c r="K11" s="13">
+        <f>K9*H11/H9</f>
+        <v>0.11164518988204816</v>
+      </c>
+      <c r="L11" s="15">
+        <v>7200000000</v>
+      </c>
+      <c r="M11">
+        <v>25</v>
+      </c>
+      <c r="N11" s="15">
+        <f t="shared" ref="N11" si="8">L11*M11*(1-I11)</f>
+        <v>163923092656.98508</v>
+      </c>
+      <c r="O11" s="15">
+        <f t="shared" ref="O11" si="9">L11*M11*(1-K11)</f>
+        <v>159903865821.23132</v>
+      </c>
+      <c r="P11" s="15">
+        <f t="shared" ref="P11" si="10">L11*M11*(1-J11)</f>
+        <v>166602577214.15421</v>
+      </c>
+    </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="O12" s="11"/>
     </row>
@@ -6653,6 +6719,23 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C23" s="14">
+        <f>3.6/(0.152*48)</f>
+        <v>0.49342105263157898</v>
+      </c>
+      <c r="D23" s="14">
+        <f>C23*0.9</f>
+        <v>0.44407894736842107</v>
+      </c>
+      <c r="E23" s="14">
+        <f>C23*1.1</f>
+        <v>0.54276315789473695</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
         <v>183</v>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-ships.xlsx
+++ b/premise/data/additional_inventories/lci-ships.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79BDFBC-15F6-A849-92C7-44ACDC21BD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F426A898-438A-DF44-8F37-3DD825F25669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10500" yWindow="660" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inventories" sheetId="1" r:id="rId1"/>
@@ -209,9 +209,6 @@
     <t>transport, freight, sea, container ship, powered with liquid ammonia</t>
   </si>
   <si>
-    <t>ammonia production, hydrogen from electrolysis</t>
-  </si>
-  <si>
     <t>ammonia, anhydrous, liquid</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>20% penalty of load carrying capacity, due to the low gravimetric density of methanol.</t>
   </si>
   <si>
-    <t>methanol distillation, hydrogen from electrolysis, CO2 from DAC</t>
-  </si>
-  <si>
     <t>methanol, purified</t>
   </si>
   <si>
@@ -383,9 +377,6 @@
     <t>Dinitrogen monoxide</t>
   </si>
   <si>
-    <t>liquefied petroleum gas production, from methanol, hydrogen from electrolysis, CO2 from DAC, energy allocation</t>
-  </si>
-  <si>
     <t>liquefied petroleum gas, synthetic</t>
   </si>
   <si>
@@ -542,9 +533,6 @@
     <t>Based on the ecoinvent dataset transport, freight, sea, container ship, to which we add an input of synthetic diesel and corresponding emissions. We assume a similar tank-to-wake efficiency as that of a martime oil-powered ship.</t>
   </si>
   <si>
-    <t>diesel production, synthetic, Fischer Tropsch process, hydrogen from electrolysis, energy allocation</t>
-  </si>
-  <si>
     <t>Assumes similar efficiency as with an oil-powered ship. Diesel LHV: 43 MJ/kg.</t>
   </si>
   <si>
@@ -636,6 +624,18 @@
   </si>
   <si>
     <t>9% penalty of load carrying capacity, due to the low gravimetric density of LPG.</t>
+  </si>
+  <si>
+    <t>diesel production, synthetic, Fischer Tropsch process, market-average hydrogen, energy allocation</t>
+  </si>
+  <si>
+    <t>liquefied petroleum gas production, from methanol, market-average hydrogen, CO2 from DAC, energy allocation</t>
+  </si>
+  <si>
+    <t>methanol distillation, market-average hydrogen, CO2 from DAC</t>
+  </si>
+  <si>
+    <t>ammonia production, with market-average hydrogen</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1085,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1093,7 +1093,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1122,7 +1122,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B10">
         <f>parameters!N7</f>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B11">
         <f>parameters!O7</f>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B12">
         <f>parameters!P7</f>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B13" s="13">
         <f>parameters!I7</f>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B14" s="13">
         <f>parameters!J7</f>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B15" s="13">
         <f>parameters!K7</f>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B16" s="13">
         <f>parameters!$C$15</f>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B17" s="13">
         <f>parameters!C18</f>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B18" s="13">
         <f>parameters!D18</f>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B19" s="13">
         <f>parameters!E18</f>
@@ -1297,7 +1297,7 @@
         <v>41</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I23" s="5">
         <v>5</v>
@@ -1455,7 +1455,7 @@
         <v>43</v>
       </c>
       <c r="H27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -1494,7 +1494,7 @@
         <v>49</v>
       </c>
       <c r="H28" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -1549,13 +1549,13 @@
         <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F30" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -1577,7 +1577,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -1614,7 +1614,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B38" s="15">
         <f>parameters!N8</f>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B39" s="15">
         <f>parameters!O8</f>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B40">
         <f>parameters!P8</f>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B41" s="13">
         <f>parameters!I8</f>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B42" s="13">
         <f>parameters!J8</f>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B43" s="13">
         <f>parameters!K8</f>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B44" s="13">
         <f>parameters!$C$15</f>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B45" s="13">
         <f>parameters!C19</f>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B46" s="13">
         <f>parameters!D19</f>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B47" s="13">
         <f>parameters!E19</f>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="51" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B51" s="17">
         <f>0.11*(B44/B45)/3.6/(1-B41)</f>
@@ -1789,7 +1789,7 @@
         <v>22</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I51">
         <v>5</v>
@@ -1961,7 +1961,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -1969,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
@@ -1998,7 +1998,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B63">
         <f>parameters!N6</f>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B64">
         <f>parameters!O6</f>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B65">
         <f>parameters!P6</f>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B66" s="13">
         <f>parameters!I6</f>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B67" s="13">
         <f>parameters!J6</f>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B68" s="13">
         <f>parameters!K6</f>
@@ -2052,7 +2052,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B69" s="13">
         <f>parameters!$C$15</f>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B70" s="13">
         <f>parameters!C17</f>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B71" s="13">
         <f>parameters!D17</f>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B72" s="13">
         <f>parameters!E17</f>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="76" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
       <c r="B76" s="12">
         <f>(0.11*(B69/B70))/18.6/(1-B66)</f>
@@ -2170,10 +2170,10 @@
         <v>17</v>
       </c>
       <c r="G76" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I76">
         <v>5</v>
@@ -2212,7 +2212,7 @@
         <v>32</v>
       </c>
       <c r="H77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I77">
         <v>5</v>
@@ -2251,7 +2251,7 @@
         <v>43</v>
       </c>
       <c r="H78" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I78">
         <v>5</v>
@@ -2290,7 +2290,7 @@
         <v>49</v>
       </c>
       <c r="H79" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I79">
         <v>5</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B81">
         <f>0.00013*(B76*18.6*B70/3.6)</f>
@@ -2350,7 +2350,7 @@
         <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I81">
         <v>5</v>
@@ -2386,7 +2386,7 @@
         <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I82">
         <v>5</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="83" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B83">
         <f>0.00002*(B76*18.6*B70/3.6)</f>
@@ -2422,7 +2422,7 @@
         <v>20</v>
       </c>
       <c r="H83" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I83">
         <v>5</v>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="84" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B84">
         <f>0.0000028*(B76*18.6*B70/3.6)</f>
@@ -2458,7 +2458,7 @@
         <v>20</v>
       </c>
       <c r="H84" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I84">
         <v>5</v>
@@ -2494,7 +2494,7 @@
         <v>20</v>
       </c>
       <c r="H85" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I85">
         <v>5</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="86" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B86">
         <f>0.000046*(B76*18.6*B70/3.6)</f>
@@ -2530,7 +2530,7 @@
         <v>20</v>
       </c>
       <c r="H86" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I86">
         <v>5</v>
@@ -2557,7 +2557,7 @@
         <v>3</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
@@ -2565,7 +2565,7 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
@@ -2602,7 +2602,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B94">
         <f>parameters!N5</f>
@@ -2611,7 +2611,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B95">
         <f>parameters!O5</f>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B96">
         <f>parameters!P5</f>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B97" s="13">
         <f>parameters!I5</f>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B98" s="13">
         <f>parameters!J5</f>
@@ -2647,7 +2647,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B99" s="13">
         <f>parameters!K5</f>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B100" s="13">
         <f>parameters!$C$15</f>
@@ -2665,7 +2665,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B101" s="13">
         <f>parameters!C16</f>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B102" s="13">
         <f>parameters!D16</f>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B103" s="13">
         <f>parameters!E16</f>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="107" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="B107" s="12">
         <f>0.11*(B100/B101)/19.9/(1-B97)</f>
@@ -2774,10 +2774,10 @@
         <v>17</v>
       </c>
       <c r="G107" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H107" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I107">
         <v>5</v>
@@ -2816,7 +2816,7 @@
         <v>43</v>
       </c>
       <c r="H108" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I108">
         <v>5</v>
@@ -2855,7 +2855,7 @@
         <v>49</v>
       </c>
       <c r="H109" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I109">
         <v>5</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="111" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B111" s="12">
         <f>B107*1.37</f>
@@ -2915,7 +2915,7 @@
         <v>20</v>
       </c>
       <c r="H111" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I111">
         <v>5</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="112" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B112" s="11">
         <f>0.0048*(B107*19.9*B101/3.6)</f>
@@ -2951,7 +2951,7 @@
         <v>20</v>
       </c>
       <c r="H112" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I112">
         <v>5</v>
@@ -2987,7 +2987,7 @@
         <v>20</v>
       </c>
       <c r="H113" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I113">
         <v>5</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="114" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B114">
         <f>0.00695*B107*0.9</f>
@@ -3023,7 +3023,7 @@
         <v>20</v>
       </c>
       <c r="H114" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I114">
         <v>5</v>
@@ -3059,7 +3059,7 @@
         <v>20</v>
       </c>
       <c r="H115" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I115">
         <v>5</v>
@@ -3087,7 +3087,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
@@ -3095,7 +3095,7 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
@@ -3103,7 +3103,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
@@ -3132,7 +3132,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B123" s="11">
         <f>parameters!N10</f>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B124" s="11">
         <f>parameters!O10</f>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B125" s="11">
         <f>parameters!P10</f>
@@ -3159,7 +3159,7 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B126" s="13">
         <f>parameters!I10</f>
@@ -3168,7 +3168,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B127" s="13">
         <f>parameters!J10</f>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B128" s="13">
         <f>parameters!K10</f>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B129" s="13">
         <f>parameters!$C$15</f>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B130" s="13">
         <f>parameters!C21</f>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B131" s="13">
         <f>parameters!D21</f>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B132" s="13">
         <f>parameters!E21</f>
@@ -3288,7 +3288,7 @@
     </row>
     <row r="136" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B136" s="12">
         <f>0.11*(B129/B130)/47.5/(1-B126)</f>
@@ -3304,10 +3304,10 @@
         <v>17</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H136" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I136">
         <v>5</v>
@@ -3346,7 +3346,7 @@
         <v>43</v>
       </c>
       <c r="H137" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I137">
         <v>5</v>
@@ -3385,7 +3385,7 @@
         <v>49</v>
       </c>
       <c r="H138" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I138">
         <v>5</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="140" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B140" s="12">
         <f>B136*2.74</f>
@@ -3445,7 +3445,7 @@
         <v>20</v>
       </c>
       <c r="H140" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I140">
         <v>5</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="141" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B141" s="11">
         <f>0.00186*(B136*48*B130/3.6)</f>
@@ -3481,7 +3481,7 @@
         <v>20</v>
       </c>
       <c r="H141" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I141">
         <v>5</v>
@@ -3517,7 +3517,7 @@
         <v>20</v>
       </c>
       <c r="H142" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I142">
         <v>5</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="143" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B143" s="11">
         <f>0.00003*(B136*48*B130/3.6)</f>
@@ -3553,7 +3553,7 @@
         <v>20</v>
       </c>
       <c r="H143" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I143">
         <v>5</v>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="144" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B144" s="11">
         <f>0.00003*(B136*48*B130/3.6)</f>
@@ -3589,7 +3589,7 @@
         <v>20</v>
       </c>
       <c r="H144" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I144">
         <v>5</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="145" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B145" s="11">
         <f>B136*0.02</f>
@@ -3625,7 +3625,7 @@
         <v>20</v>
       </c>
       <c r="H145" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I145">
         <v>5</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="146" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B146" s="11">
         <f>0.00038*(B136*48*B130/3.6)</f>
@@ -3661,7 +3661,7 @@
         <v>20</v>
       </c>
       <c r="H146" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I146">
         <v>5</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="147" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B147" s="11">
         <f>0.00002*(B136*48*B130/3.6)</f>
@@ -3697,7 +3697,7 @@
         <v>20</v>
       </c>
       <c r="H147" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I147">
         <v>5</v>
@@ -3720,7 +3720,7 @@
         <v>3</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
@@ -3728,7 +3728,7 @@
         <v>11</v>
       </c>
       <c r="B151" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
@@ -3736,7 +3736,7 @@
         <v>10</v>
       </c>
       <c r="B152" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
@@ -3765,7 +3765,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B156" s="11">
         <f>parameters!N11</f>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B157" s="11">
         <f>parameters!O11</f>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B158" s="11">
         <f>parameters!P11</f>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B159" s="13">
         <f>parameters!I11</f>
@@ -3801,7 +3801,7 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B160" s="13">
         <f>parameters!J11</f>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B161" s="13">
         <f>parameters!K11</f>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B162" s="13">
         <f>parameters!$C$15</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B163" s="13">
         <f>parameters!C23</f>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B164" s="13">
         <f>parameters!D23</f>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B165" s="13">
         <f>parameters!E23</f>
@@ -3921,7 +3921,7 @@
     </row>
     <row r="169" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="B169" s="12">
         <f>0.11*(B162/B163)/46/(1-B159)</f>
@@ -3937,10 +3937,10 @@
         <v>17</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H169" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I169">
         <v>5</v>
@@ -3979,7 +3979,7 @@
         <v>43</v>
       </c>
       <c r="H170" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I170">
         <v>5</v>
@@ -4018,7 +4018,7 @@
         <v>49</v>
       </c>
       <c r="H171" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I171">
         <v>5</v>
@@ -4062,7 +4062,7 @@
     </row>
     <row r="173" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B173" s="12">
         <f>B169*3</f>
@@ -4078,7 +4078,7 @@
         <v>20</v>
       </c>
       <c r="H173" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I173">
         <v>5</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="174" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B174" s="11">
         <f>0.00186*(B169*46*B163/3.6)</f>
@@ -4114,7 +4114,7 @@
         <v>20</v>
       </c>
       <c r="H174" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I174">
         <v>5</v>
@@ -4150,7 +4150,7 @@
         <v>20</v>
       </c>
       <c r="H175" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I175">
         <v>5</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="176" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B176" s="11">
         <f>0.00003*(B169*46*B163/3.6)</f>
@@ -4186,7 +4186,7 @@
         <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I176">
         <v>5</v>
@@ -4206,7 +4206,7 @@
     </row>
     <row r="177" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B177" s="11">
         <f>0.00003*(B169*46*B163/3.6)</f>
@@ -4222,7 +4222,7 @@
         <v>20</v>
       </c>
       <c r="H177" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I177">
         <v>5</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="178" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B178" s="11">
         <f>B169*0.02</f>
@@ -4258,7 +4258,7 @@
         <v>20</v>
       </c>
       <c r="H178" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I178">
         <v>5</v>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="179" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B179" s="11">
         <f>0.00038*(B169*46*B163/3.6)</f>
@@ -4294,7 +4294,7 @@
         <v>20</v>
       </c>
       <c r="H179" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I179">
         <v>5</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="180" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B180" s="11">
         <f>0.00002*(B169*46*B163/3.6)</f>
@@ -4330,7 +4330,7 @@
         <v>20</v>
       </c>
       <c r="H180" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I180">
         <v>5</v>
@@ -4353,7 +4353,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
@@ -4361,7 +4361,7 @@
         <v>11</v>
       </c>
       <c r="B183" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
@@ -4369,7 +4369,7 @@
         <v>10</v>
       </c>
       <c r="B184" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
@@ -4398,7 +4398,7 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B188" s="11">
         <f>parameters!N4</f>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B189" s="11">
         <f>parameters!O4</f>
@@ -4416,7 +4416,7 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B190" s="11">
         <f>parameters!P4</f>
@@ -4425,7 +4425,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B191" s="13">
         <v>0</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B192" s="13">
         <v>0</v>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B193" s="13">
         <v>0</v>
@@ -4449,7 +4449,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B194" s="13">
         <f>parameters!$C$15</f>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B195" s="13">
         <f>parameters!C22</f>
@@ -4467,7 +4467,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B196" s="13">
         <f>parameters!D22</f>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B197" s="13">
         <f>parameters!E22</f>
@@ -4551,14 +4551,14 @@
     </row>
     <row r="201" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B201" s="12">
         <f>0.11*(B194/B195)/46/(1-B191)</f>
         <v>2.0151056763285029E-3</v>
       </c>
       <c r="C201" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
@@ -4567,10 +4567,10 @@
         <v>17</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H201" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I201">
         <v>5</v>
@@ -4609,7 +4609,7 @@
         <v>43</v>
       </c>
       <c r="H202" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J202" s="11"/>
       <c r="K202" s="11"/>
@@ -4636,7 +4636,7 @@
         <v>49</v>
       </c>
       <c r="H203" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J203" s="11"/>
       <c r="K203" s="11"/>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="205" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B205" s="12">
         <f>B201*3.15</f>
@@ -4684,7 +4684,7 @@
         <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I205">
         <v>5</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="206" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B206" s="11">
         <f>0.0009*(B201*43*B195/3.6)</f>
@@ -4720,7 +4720,7 @@
         <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I206">
         <v>5</v>
@@ -4756,7 +4756,7 @@
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I207">
         <v>5</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="208" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B208" s="11">
         <f>0.0000163*0.2</f>
@@ -4792,7 +4792,7 @@
         <v>20</v>
       </c>
       <c r="H208" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I208">
         <v>5</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="209" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B209" s="11">
         <f>0.00001*(B201*43*B195/3.6)</f>
@@ -4828,7 +4828,7 @@
         <v>20</v>
       </c>
       <c r="H209" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I209">
         <v>5</v>
@@ -4848,7 +4848,7 @@
     </row>
     <row r="210" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B210" s="11">
         <f>0.00041*(B201*43*B195/3.6)</f>
@@ -4864,7 +4864,7 @@
         <v>20</v>
       </c>
       <c r="H210" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I210">
         <v>5</v>
@@ -4884,7 +4884,7 @@
     </row>
     <row r="211" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B211" s="11">
         <f>0.00003*(B201*43*B195/3.6)</f>
@@ -4900,7 +4900,7 @@
         <v>20</v>
       </c>
       <c r="H211" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I211">
         <v>5</v>
@@ -4923,7 +4923,7 @@
         <v>3</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
@@ -4931,7 +4931,7 @@
         <v>11</v>
       </c>
       <c r="B214" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
@@ -4939,7 +4939,7 @@
         <v>10</v>
       </c>
       <c r="B215" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
@@ -4968,7 +4968,7 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B219" s="11">
         <f>parameters!N4</f>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B220" s="11">
         <f>parameters!O4</f>
@@ -4986,7 +4986,7 @@
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B221" s="11">
         <f>parameters!P4</f>
@@ -4995,7 +4995,7 @@
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B222" s="13">
         <f>parameters!I41</f>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B223" s="13">
         <f>parameters!J41</f>
@@ -5013,7 +5013,7 @@
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B224" s="13">
         <f>parameters!K41</f>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B225" s="13">
         <f>parameters!$C$15</f>
@@ -5031,7 +5031,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B226" s="13">
         <f>parameters!C22</f>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B227" s="13">
         <f>parameters!D22</f>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B228" s="13">
         <f>parameters!E22</f>
@@ -5124,7 +5124,7 @@
     </row>
     <row r="232" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="B232" s="12">
         <f>0.11*(B225/B226)/46/(1-B222)</f>
@@ -5140,10 +5140,10 @@
         <v>17</v>
       </c>
       <c r="G232" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H232" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I232">
         <v>5</v>
@@ -5182,7 +5182,7 @@
         <v>43</v>
       </c>
       <c r="H233" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J233" s="11"/>
       <c r="K233" s="11"/>
@@ -5209,7 +5209,7 @@
         <v>49</v>
       </c>
       <c r="H234" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J234" s="11"/>
       <c r="K234" s="11"/>
@@ -5241,7 +5241,7 @@
     </row>
     <row r="236" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B236" s="12">
         <f>B232*3.15</f>
@@ -5257,7 +5257,7 @@
         <v>20</v>
       </c>
       <c r="H236" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I236">
         <v>5</v>
@@ -5277,7 +5277,7 @@
     </row>
     <row r="237" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B237" s="11">
         <f>0.0009*(B232*43*B226/3.6)</f>
@@ -5293,7 +5293,7 @@
         <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I237">
         <v>5</v>
@@ -5329,7 +5329,7 @@
         <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I238">
         <v>5</v>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="239" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B239" s="11">
         <f>0.0000163*0.2</f>
@@ -5365,7 +5365,7 @@
         <v>20</v>
       </c>
       <c r="H239" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I239">
         <v>5</v>
@@ -5385,7 +5385,7 @@
     </row>
     <row r="240" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B240" s="11">
         <f>0.00001*(B232*43*B226/3.6)</f>
@@ -5401,7 +5401,7 @@
         <v>20</v>
       </c>
       <c r="H240" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I240">
         <v>5</v>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="241" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B241" s="11">
         <f>0.00041*(B232*43*B226/3.6)</f>
@@ -5437,7 +5437,7 @@
         <v>20</v>
       </c>
       <c r="H241" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I241">
         <v>5</v>
@@ -5457,7 +5457,7 @@
     </row>
     <row r="242" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B242" s="11">
         <f>0.00003*(B232*43*B226/3.6)</f>
@@ -5473,7 +5473,7 @@
         <v>20</v>
       </c>
       <c r="H242" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I242">
         <v>5</v>
@@ -5496,7 +5496,7 @@
         <v>3</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
@@ -5504,7 +5504,7 @@
         <v>11</v>
       </c>
       <c r="B245" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
@@ -5512,7 +5512,7 @@
         <v>10</v>
       </c>
       <c r="B246" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.2">
@@ -5541,7 +5541,7 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B250" s="11">
         <f>parameters!N4</f>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B251" s="11">
         <f>parameters!O4</f>
@@ -5559,7 +5559,7 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B252" s="11">
         <f>parameters!P4</f>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B253" s="13">
         <f>parameters!I72</f>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B254" s="13">
         <f>parameters!J72</f>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B255" s="13">
         <f>parameters!K72</f>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B256" s="13">
         <f>parameters!$C$15</f>
@@ -5604,7 +5604,7 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B257" s="13">
         <f>parameters!C22</f>
@@ -5613,7 +5613,7 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B258" s="13">
         <f>parameters!D22</f>
@@ -5622,7 +5622,7 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B259" s="13">
         <f>parameters!E22</f>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="263" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B263" s="12">
         <f>0.11*(B256/B257)/46/(1-B253)</f>
@@ -5713,10 +5713,10 @@
         <v>17</v>
       </c>
       <c r="G263" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H263" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I263">
         <v>5</v>
@@ -5755,7 +5755,7 @@
         <v>43</v>
       </c>
       <c r="H264" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J264" s="11"/>
       <c r="K264" s="11"/>
@@ -5782,7 +5782,7 @@
         <v>49</v>
       </c>
       <c r="H265" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J265" s="11"/>
       <c r="K265" s="11"/>
@@ -5814,7 +5814,7 @@
     </row>
     <row r="267" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B267" s="12">
         <f>B263*3.15</f>
@@ -5830,7 +5830,7 @@
         <v>20</v>
       </c>
       <c r="H267" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I267">
         <v>5</v>
@@ -5850,7 +5850,7 @@
     </row>
     <row r="268" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B268" s="11">
         <f>0.0009*(B263*43*B257/3.6)</f>
@@ -5866,7 +5866,7 @@
         <v>20</v>
       </c>
       <c r="H268" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I268">
         <v>5</v>
@@ -5902,7 +5902,7 @@
         <v>20</v>
       </c>
       <c r="H269" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I269">
         <v>5</v>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="270" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B270" s="11">
         <f>0.0000163*0.2</f>
@@ -5938,7 +5938,7 @@
         <v>20</v>
       </c>
       <c r="H270" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I270">
         <v>5</v>
@@ -5958,7 +5958,7 @@
     </row>
     <row r="271" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B271" s="11">
         <f>0.00001*(B263*43*B257/3.6)</f>
@@ -5974,7 +5974,7 @@
         <v>20</v>
       </c>
       <c r="H271" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I271">
         <v>5</v>
@@ -5994,7 +5994,7 @@
     </row>
     <row r="272" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B272" s="11">
         <f>0.00041*(B263*43*B257/3.6)</f>
@@ -6010,7 +6010,7 @@
         <v>20</v>
       </c>
       <c r="H272" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I272">
         <v>5</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="273" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B273" s="11">
         <f>0.00003*(B263*43*B257/3.6)</f>
@@ -6046,7 +6046,7 @@
         <v>20</v>
       </c>
       <c r="H273" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I273">
         <v>5</v>
@@ -6096,62 +6096,62 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="E3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="I3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D4" s="16">
         <v>1</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D5" s="16">
         <v>0.43880000000000002</v>
@@ -6249,10 +6249,10 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" s="16">
         <v>0.35270000000000001</v>
@@ -6303,10 +6303,10 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D7" s="16">
         <v>0.25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D8" s="16">
         <v>8.3300000000000006E-3</v>
@@ -6411,10 +6411,10 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D9" s="16">
         <v>0.61109999999999998</v>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D10" s="16">
         <v>0.27700000000000002</v>
@@ -6517,10 +6517,10 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D11" s="16">
         <f>26.5/36</f>
@@ -6577,21 +6577,21 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C15" s="14">
         <f>AVERAGE(D15:E15)</f>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16" s="14">
         <f>3.6/(0.414*19.9)</f>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" s="14">
         <f>3.6/(0.435*18.8)</f>
@@ -6638,7 +6638,7 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C18" s="14">
         <f>AVERAGE(D18:E18)</f>
@@ -6653,7 +6653,7 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C19" s="14">
         <f>AVERAGE(D19:E19)</f>
@@ -6668,7 +6668,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C20" s="14">
         <f>3.6/(0.152*48)</f>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C21" s="14">
         <f>3.6/(0.152*48)</f>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C22" s="14">
         <f>3.6/(0.166*43)</f>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C23" s="14">
         <f>3.6/(0.152*48)</f>
@@ -6736,7 +6736,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/premise/data/additional_inventories/lci-ships.xlsx
+++ b/premise/data/additional_inventories/lci-ships.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ac145674\coding_projects\premise_h2-distribution\premise\data\additional_inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F426A898-438A-DF44-8F37-3DD825F25669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA23D2A4-BEA8-4936-BBFE-826CDCD39D6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10500" yWindow="660" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10500" yWindow="660" windowWidth="25824" windowHeight="18984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inventories" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">inventories!$A$1:$O$225</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -643,13 +631,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -710,7 +698,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
@@ -718,12 +706,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -732,17 +720,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Komma" xfId="1" builtinId="3"/>
+    <cellStyle name="Prozent" xfId="2" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -758,9 +746,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -798,9 +786,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -833,9 +821,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -868,9 +873,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1045,18 +1067,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O273"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="62.1640625" customWidth="1"/>
+    <col min="1" max="1" width="62.109375" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="22.77734375" customWidth="1"/>
     <col min="8" max="8" width="56" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1064,7 +1086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1072,7 +1094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="15.6">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1080,7 +1102,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1088,7 +1110,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1096,7 +1118,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1104,7 +1126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1112,7 +1134,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1120,7 +1142,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -1129,7 +1151,7 @@
         <v>121500000000.00002</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>92</v>
       </c>
@@ -1138,7 +1160,7 @@
         <v>108000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -1147,7 +1169,7 @@
         <v>135000000000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>153</v>
       </c>
@@ -1156,7 +1178,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>154</v>
       </c>
@@ -1165,7 +1187,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>155</v>
       </c>
@@ -1174,7 +1196,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>131</v>
       </c>
@@ -1183,7 +1205,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>128</v>
       </c>
@@ -1192,7 +1214,7 @@
         <v>0.47500000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>129</v>
       </c>
@@ -1201,7 +1223,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -1210,12 +1232,12 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="15.6">
       <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15">
       <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
@@ -1253,7 +1275,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15">
       <c r="A22" t="str">
         <f>B4</f>
         <v>transport, freight, sea, container ship, powered with hydrogen</v>
@@ -1276,7 +1298,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" s="5" customFormat="1" ht="15.6">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -1317,7 +1339,7 @@
       <c r="M23"/>
       <c r="O23" s="7"/>
     </row>
-    <row r="24" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="15.6">
       <c r="A24" s="8" t="s">
         <v>27</v>
       </c>
@@ -1356,7 +1378,7 @@
         <v>2.3148148148148148E-8</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1395,7 +1417,7 @@
         <v>2.7777777777777779E-6</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1434,7 +1456,7 @@
         <v>9.2592592592592591E-6</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -1473,7 +1495,7 @@
         <v>9.2592592592592589E-12</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -1512,7 +1534,7 @@
         <v>9.2592592592592589E-12</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1536,7 +1558,7 @@
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -1561,10 +1583,10 @@
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15">
       <c r="B31" s="11"/>
     </row>
-    <row r="32" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="15.6">
       <c r="A32" s="1" t="s">
         <v>3</v>
       </c>
@@ -1572,7 +1594,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -1580,7 +1602,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1588,7 +1610,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1596,7 +1618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -1604,7 +1626,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1612,7 +1634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -1621,7 +1643,7 @@
         <v>90000000000</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -1630,7 +1652,7 @@
         <v>72000000000</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>93</v>
       </c>
@@ -1639,7 +1661,7 @@
         <v>108000000000</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>153</v>
       </c>
@@ -1648,7 +1670,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>154</v>
       </c>
@@ -1657,7 +1679,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>155</v>
       </c>
@@ -1666,7 +1688,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>131</v>
       </c>
@@ -1675,7 +1697,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>128</v>
       </c>
@@ -1684,7 +1706,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>129</v>
       </c>
@@ -1693,7 +1715,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>130</v>
       </c>
@@ -1702,12 +1724,12 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="15.6">
       <c r="A48" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12">
       <c r="A49" s="2" t="s">
         <v>13</v>
       </c>
@@ -1745,7 +1767,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12">
       <c r="A50" t="str">
         <f>B32</f>
         <v>transport, freight, sea, container ship, powered with electricity</v>
@@ -1768,7 +1790,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="15.6">
       <c r="A51" t="s">
         <v>151</v>
       </c>
@@ -1807,7 +1829,7 @@
         <v>4.3287037037037041E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
         <v>31</v>
       </c>
@@ -1846,7 +1868,7 @@
         <v>1.3888888888888889E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
         <v>44</v>
       </c>
@@ -1885,7 +1907,7 @@
         <v>1.3888888888888888E-11</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -1924,7 +1946,7 @@
         <v>1.3888888888888888E-11</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
         <v>52</v>
       </c>
@@ -1948,7 +1970,7 @@
       <c r="K55" s="11"/>
       <c r="L55" s="11"/>
     </row>
-    <row r="57" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="15.6">
       <c r="A57" s="1" t="s">
         <v>3</v>
       </c>
@@ -1956,7 +1978,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -1964,7 +1986,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -1972,7 +1994,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -1980,7 +2002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1988,7 +2010,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -1996,7 +2018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2005,7 +2027,7 @@
         <v>144000000000</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -2014,7 +2036,7 @@
         <v>135000000000</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -2023,7 +2045,7 @@
         <v>153000000000</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
         <v>153</v>
       </c>
@@ -2032,7 +2054,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
         <v>154</v>
       </c>
@@ -2041,7 +2063,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
         <v>155</v>
       </c>
@@ -2050,7 +2072,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12">
       <c r="A69" t="s">
         <v>131</v>
       </c>
@@ -2059,7 +2081,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12">
       <c r="A70" t="s">
         <v>128</v>
       </c>
@@ -2068,7 +2090,7 @@
         <v>0.44020542920029343</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
         <v>129</v>
       </c>
@@ -2077,7 +2099,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12">
       <c r="A72" t="s">
         <v>130</v>
       </c>
@@ -2086,12 +2108,12 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="15.6">
       <c r="A73" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12">
       <c r="A74" s="2" t="s">
         <v>13</v>
       </c>
@@ -2129,7 +2151,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12">
       <c r="A75" t="str">
         <f>B57</f>
         <v>transport, freight, sea, container ship, powered with liquid ammonia</v>
@@ -2152,7 +2174,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="15.6">
       <c r="A76" t="s">
         <v>199</v>
       </c>
@@ -2191,7 +2213,7 @@
         <v>9.5750128008192537E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12">
       <c r="A77" t="s">
         <v>31</v>
       </c>
@@ -2230,7 +2252,7 @@
         <v>7.4074074074074073E-8</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12">
       <c r="A78" t="s">
         <v>44</v>
       </c>
@@ -2269,7 +2291,7 @@
         <v>7.4074074074074068E-12</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12">
       <c r="A79" t="s">
         <v>50</v>
       </c>
@@ -2308,7 +2330,7 @@
         <v>7.4074074074074068E-12</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12">
       <c r="A80" t="s">
         <v>52</v>
       </c>
@@ -2332,7 +2354,7 @@
       <c r="K80" s="11"/>
       <c r="L80" s="11"/>
     </row>
-    <row r="81" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="15.6">
       <c r="A81" t="s">
         <v>60</v>
       </c>
@@ -2368,7 +2390,7 @@
         <v>2.1571959635416667E-6</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="15.6">
       <c r="A82" t="s">
         <v>24</v>
       </c>
@@ -2404,7 +2426,7 @@
         <v>4.3143919270833341E-5</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="15.6">
       <c r="A83" t="s">
         <v>61</v>
       </c>
@@ -2440,7 +2462,7 @@
         <v>3.3187630208333344E-7</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="15.6">
       <c r="A84" t="s">
         <v>62</v>
       </c>
@@ -2468,15 +2490,15 @@
         <v>4.5451388888888888E-8</v>
       </c>
       <c r="K84" s="6">
-        <f>0.0000028*(B76*18.6*B71/3.6)</f>
-        <v>3.6137641782407408E-8</v>
+        <f t="shared" ref="K84:K86" si="2">0.00002*(B77*18.6*B72/3.6)</f>
+        <v>1.6145833333333334E-12</v>
       </c>
       <c r="L84" s="6">
         <f>0.0000028*(B76*18.6*B72/3.6)</f>
         <v>4.6462682291666672E-8</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="15.6">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -2504,15 +2526,15 @@
         <v>6.4930555555555568E-7</v>
       </c>
       <c r="K85" s="6">
-        <f>0.00004*(B76*18.6*B71/3.6)</f>
-        <v>5.1625202546296308E-7</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L85" s="6">
         <f>0.00004*(B76*18.6*B72/3.6)</f>
         <v>6.6375260416666688E-7</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="15.6">
       <c r="A86" t="s">
         <v>112</v>
       </c>
@@ -2539,20 +2561,20 @@
         <f t="shared" si="1"/>
         <v>7.4670138888888891E-7</v>
       </c>
-      <c r="K86" s="11">
-        <f>0.00001*(B76*18.6*B71/3.6)</f>
-        <v>1.2906300636574077E-7</v>
+      <c r="K86" s="6" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
       </c>
       <c r="L86">
         <f>0.00013*(B76*18.6*B72/3.6)</f>
         <v>2.1571959635416667E-6</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="15.6">
       <c r="J87" s="6"/>
       <c r="K87" s="11"/>
     </row>
-    <row r="88" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="15.6">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -2560,7 +2582,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -2568,7 +2590,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -2576,7 +2598,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2584,7 +2606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -2592,7 +2614,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -2600,7 +2622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
         <v>91</v>
       </c>
@@ -2609,7 +2631,7 @@
         <v>144000000000</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
         <v>92</v>
       </c>
@@ -2618,7 +2640,7 @@
         <v>135000000000</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
         <v>93</v>
       </c>
@@ -2627,7 +2649,7 @@
         <v>153000000000</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12">
       <c r="A97" t="s">
         <v>153</v>
       </c>
@@ -2636,7 +2658,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12">
       <c r="A98" t="s">
         <v>154</v>
       </c>
@@ -2645,7 +2667,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12">
       <c r="A99" t="s">
         <v>155</v>
       </c>
@@ -2654,7 +2676,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12">
       <c r="A100" t="s">
         <v>131</v>
       </c>
@@ -2663,7 +2685,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12">
       <c r="A101" t="s">
         <v>128</v>
       </c>
@@ -2672,7 +2694,7 @@
         <v>0.4369674459252787</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12">
       <c r="A102" t="s">
         <v>129</v>
       </c>
@@ -2681,7 +2703,7 @@
         <v>0.32772558444395905</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12">
       <c r="A103" t="s">
         <v>130</v>
       </c>
@@ -2690,12 +2712,12 @@
         <v>0.54620930740659834</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="15.6">
       <c r="A104" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12">
       <c r="A105" s="2" t="s">
         <v>13</v>
       </c>
@@ -2733,7 +2755,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12">
       <c r="A106" t="str">
         <f>B88</f>
         <v>transport, freight, sea, container ship, powered with methanol</v>
@@ -2756,7 +2778,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="15.6">
       <c r="A107" t="s">
         <v>198</v>
       </c>
@@ -2795,7 +2817,7 @@
         <v>9.5577777777777744E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12">
       <c r="A108" t="s">
         <v>44</v>
       </c>
@@ -2834,7 +2856,7 @@
         <v>7.4074074074074068E-12</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12">
       <c r="A109" t="s">
         <v>50</v>
       </c>
@@ -2873,7 +2895,7 @@
         <v>7.4074074074074068E-12</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12">
       <c r="A110" t="s">
         <v>52</v>
       </c>
@@ -2897,7 +2919,7 @@
       <c r="K110" s="11"/>
       <c r="L110" s="11"/>
     </row>
-    <row r="111" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="15.6">
       <c r="A111" t="s">
         <v>67</v>
       </c>
@@ -2933,7 +2955,7 @@
         <v>1.3094155555555553E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="15.6">
       <c r="A112" t="s">
         <v>60</v>
       </c>
@@ -2957,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="J112" s="6">
-        <f t="shared" ref="J112:J115" si="2">B112</f>
+        <f t="shared" ref="J112:J115" si="3">B112</f>
         <v>7.7916666666666672E-5</v>
       </c>
       <c r="K112" s="6">
@@ -2969,7 +2991,7 @@
         <v>9.7395833333333313E-5</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="15.6">
       <c r="A113" t="s">
         <v>24</v>
       </c>
@@ -2993,7 +3015,7 @@
         <v>5</v>
       </c>
       <c r="J113" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.3613953124999986E-5</v>
       </c>
       <c r="K113" s="6">
@@ -3005,7 +3027,7 @@
         <v>1.8722790624999997E-4</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="15.6">
       <c r="A114" t="s">
         <v>61</v>
       </c>
@@ -3029,7 +3051,7 @@
         <v>5</v>
       </c>
       <c r="J114" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.2035554687499993E-5</v>
       </c>
       <c r="K114" s="6">
@@ -3041,7 +3063,7 @@
         <v>8.4071109374999985E-5</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="15.6">
       <c r="A115" t="s">
         <v>26</v>
       </c>
@@ -3065,7 +3087,7 @@
         <v>5</v>
       </c>
       <c r="J115" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.953993055555555E-9</v>
       </c>
       <c r="K115" s="6">
@@ -3077,12 +3099,12 @@
         <v>9.9424913194444421E-9</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="15.6">
       <c r="J116" s="6"/>
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
     </row>
-    <row r="117" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="15.6">
       <c r="A117" s="1" t="s">
         <v>3</v>
       </c>
@@ -3090,7 +3112,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -3098,7 +3120,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12">
       <c r="A119" t="s">
         <v>10</v>
       </c>
@@ -3106,7 +3128,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -3114,7 +3136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12">
       <c r="A121" t="s">
         <v>6</v>
       </c>
@@ -3122,7 +3144,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12">
       <c r="A122" t="s">
         <v>8</v>
       </c>
@@ -3130,7 +3152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12">
       <c r="A123" t="s">
         <v>91</v>
       </c>
@@ -3139,7 +3161,7 @@
         <v>108000000000</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12">
       <c r="A124" t="s">
         <v>92</v>
       </c>
@@ -3148,7 +3170,7 @@
         <v>90000000000</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12">
       <c r="A125" t="s">
         <v>93</v>
       </c>
@@ -3157,7 +3179,7 @@
         <v>117000000000</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -3166,7 +3188,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -3175,7 +3197,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12">
       <c r="A128" t="s">
         <v>155</v>
       </c>
@@ -3184,7 +3206,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12">
       <c r="A129" t="s">
         <v>131</v>
       </c>
@@ -3193,7 +3215,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12">
       <c r="A130" t="s">
         <v>128</v>
       </c>
@@ -3202,7 +3224,7 @@
         <v>0.49342105263157898</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12">
       <c r="A131" t="s">
         <v>129</v>
       </c>
@@ -3211,7 +3233,7 @@
         <v>0.44407894736842107</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12">
       <c r="A132" t="s">
         <v>130</v>
       </c>
@@ -3220,12 +3242,12 @@
         <v>0.54276315789473695</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="15.6">
       <c r="A133" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12">
       <c r="A134" s="2" t="s">
         <v>13</v>
       </c>
@@ -3263,7 +3285,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12">
       <c r="A135" t="str">
         <f>B117</f>
         <v>transport, freight, sea, container ship, powered with synthetic methane</v>
@@ -3286,7 +3308,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="15.6">
       <c r="A136" t="s">
         <v>107</v>
       </c>
@@ -3325,7 +3347,7 @@
         <v>4.432592592592593E-3</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12">
       <c r="A137" t="s">
         <v>44</v>
       </c>
@@ -3364,7 +3386,7 @@
         <v>1.1111111111111111E-11</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12">
       <c r="A138" t="s">
         <v>50</v>
       </c>
@@ -3403,7 +3425,7 @@
         <v>1.1111111111111111E-11</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12">
       <c r="A139" t="s">
         <v>52</v>
       </c>
@@ -3427,7 +3449,7 @@
       <c r="K139" s="11"/>
       <c r="L139" s="11"/>
     </row>
-    <row r="140" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="15.6">
       <c r="A140" t="s">
         <v>67</v>
       </c>
@@ -3463,7 +3485,7 @@
         <v>1.2145303703703706E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="15.6">
       <c r="A141" t="s">
         <v>60</v>
       </c>
@@ -3487,7 +3509,7 @@
         <v>5</v>
       </c>
       <c r="J141" s="6">
-        <f t="shared" ref="J141:J144" si="3">B141</f>
+        <f t="shared" ref="J141:J144" si="4">B141</f>
         <v>4.0680701754385975E-5</v>
       </c>
       <c r="K141" s="6">
@@ -3499,7 +3521,7 @@
         <v>4.4748771929824572E-5</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="15.6">
       <c r="A142" t="s">
         <v>24</v>
       </c>
@@ -3523,7 +3545,7 @@
         <v>5</v>
       </c>
       <c r="J142" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5589473684210534E-5</v>
       </c>
       <c r="K142" s="6">
@@ -3535,7 +3557,7 @@
         <v>2.8148421052631585E-5</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="15.6">
       <c r="A143" t="s">
         <v>110</v>
       </c>
@@ -3559,7 +3581,7 @@
         <v>5</v>
       </c>
       <c r="J143" s="6">
-        <f t="shared" ref="J143" si="4">B143</f>
+        <f t="shared" ref="J143" si="5">B143</f>
         <v>6.5614035087719314E-7</v>
       </c>
       <c r="K143" s="6">
@@ -3571,7 +3593,7 @@
         <v>7.2175438596491244E-7</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="15.6">
       <c r="A144" t="s">
         <v>61</v>
       </c>
@@ -3595,7 +3617,7 @@
         <v>5</v>
       </c>
       <c r="J144" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.5614035087719314E-7</v>
       </c>
       <c r="K144" s="6">
@@ -3607,7 +3629,7 @@
         <v>7.2175438596491244E-7</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="15.6">
       <c r="A145" t="s">
         <v>111</v>
       </c>
@@ -3631,7 +3653,7 @@
         <v>5</v>
       </c>
       <c r="J145" s="6">
-        <f t="shared" ref="J145:J147" si="5">B145</f>
+        <f t="shared" ref="J145:J147" si="6">B145</f>
         <v>6.6488888888888891E-5</v>
       </c>
       <c r="K145" s="6">
@@ -3643,7 +3665,7 @@
         <v>2.2273777777777779E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="15.6">
       <c r="A146" t="s">
         <v>62</v>
       </c>
@@ -3667,7 +3689,7 @@
         <v>5</v>
       </c>
       <c r="J146" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.311111111111113E-6</v>
       </c>
       <c r="K146" s="6">
@@ -3679,7 +3701,7 @@
         <v>9.1422222222222249E-6</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="15.6">
       <c r="A147" t="s">
         <v>112</v>
       </c>
@@ -3703,7 +3725,7 @@
         <v>5</v>
       </c>
       <c r="J147" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.3742690058479546E-7</v>
       </c>
       <c r="K147" s="11">
@@ -3715,7 +3737,7 @@
         <v>4.81169590643275E-7</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="15.6">
       <c r="A150" s="1" t="s">
         <v>3</v>
       </c>
@@ -3723,7 +3745,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12">
       <c r="A151" t="s">
         <v>11</v>
       </c>
@@ -3731,7 +3753,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12">
       <c r="A152" t="s">
         <v>10</v>
       </c>
@@ -3739,7 +3761,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -3747,7 +3769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12">
       <c r="A154" t="s">
         <v>6</v>
       </c>
@@ -3755,7 +3777,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12">
       <c r="A155" t="s">
         <v>8</v>
       </c>
@@ -3763,7 +3785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12">
       <c r="A156" t="s">
         <v>91</v>
       </c>
@@ -3772,7 +3794,7 @@
         <v>163923092656.98508</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12">
       <c r="A157" t="s">
         <v>92</v>
       </c>
@@ -3781,7 +3803,7 @@
         <v>159903865821.23132</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12">
       <c r="A158" t="s">
         <v>93</v>
       </c>
@@ -3790,7 +3812,7 @@
         <v>166602577214.15421</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12">
       <c r="A159" t="s">
         <v>153</v>
       </c>
@@ -3799,7 +3821,7 @@
         <v>8.9316151905638519E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12">
       <c r="A160" t="s">
         <v>154</v>
       </c>
@@ -3808,7 +3830,7 @@
         <v>7.4430126588032122E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12">
       <c r="A161" t="s">
         <v>155</v>
       </c>
@@ -3817,7 +3839,7 @@
         <v>0.11164518988204816</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12">
       <c r="A162" t="s">
         <v>131</v>
       </c>
@@ -3826,7 +3848,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12">
       <c r="A163" t="s">
         <v>128</v>
       </c>
@@ -3835,7 +3857,7 @@
         <v>0.49342105263157898</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12">
       <c r="A164" t="s">
         <v>129</v>
       </c>
@@ -3844,7 +3866,7 @@
         <v>0.44407894736842107</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12">
       <c r="A165" t="s">
         <v>130</v>
       </c>
@@ -3853,12 +3875,12 @@
         <v>0.54276315789473695</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="15.6">
       <c r="A166" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12">
       <c r="A167" s="2" t="s">
         <v>13</v>
       </c>
@@ -3896,7 +3918,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12">
       <c r="A168" t="str">
         <f>B150</f>
         <v>transport, freight, sea, container ship, powered with synthetic liquefied petroleum gas</v>
@@ -3919,7 +3941,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" ht="15.6">
       <c r="A169" t="s">
         <v>197</v>
       </c>
@@ -3958,7 +3980,7 @@
         <v>2.5761855529249592E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12">
       <c r="A170" t="s">
         <v>44</v>
       </c>
@@ -3997,7 +4019,7 @@
         <v>6.25375749900866E-12</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12">
       <c r="A171" t="s">
         <v>50</v>
       </c>
@@ -4036,7 +4058,7 @@
         <v>6.25375749900866E-12</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12">
       <c r="A172" t="s">
         <v>52</v>
       </c>
@@ -4060,7 +4082,7 @@
       <c r="K172" s="11"/>
       <c r="L172" s="11"/>
     </row>
-    <row r="173" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" ht="15.6">
       <c r="A173" t="s">
         <v>67</v>
       </c>
@@ -4096,7 +4118,7 @@
         <v>7.7285566587748777E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" ht="15.6">
       <c r="A174" t="s">
         <v>60</v>
       </c>
@@ -4120,7 +4142,7 @@
         <v>5</v>
       </c>
       <c r="J174" s="6">
-        <f t="shared" ref="J174:J180" si="6">B174</f>
+        <f t="shared" ref="J174:J180" si="7">B174</f>
         <v>2.6523108669611446E-5</v>
       </c>
       <c r="K174" s="6">
@@ -4132,7 +4154,7 @@
         <v>2.9175419536572591E-5</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" ht="15.6">
       <c r="A175" t="s">
         <v>24</v>
       </c>
@@ -4156,7 +4178,7 @@
         <v>5</v>
       </c>
       <c r="J175" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6683890937336232E-5</v>
       </c>
       <c r="K175" s="6">
@@ -4168,7 +4190,7 @@
         <v>1.8352280031069855E-5</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" ht="15.6">
       <c r="A176" t="s">
         <v>110</v>
       </c>
@@ -4192,7 +4214,7 @@
         <v>5</v>
       </c>
       <c r="J176" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.2779207531631361E-7</v>
       </c>
       <c r="K176" s="6">
@@ -4204,7 +4226,7 @@
         <v>4.7057128284794499E-7</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" ht="15.6">
       <c r="A177" t="s">
         <v>61</v>
       </c>
@@ -4228,7 +4250,7 @@
         <v>5</v>
       </c>
       <c r="J177" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.2779207531631361E-7</v>
       </c>
       <c r="K177" s="6">
@@ -4240,7 +4262,7 @@
         <v>4.7057128284794499E-7</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" ht="15.6">
       <c r="A178" t="s">
         <v>111</v>
       </c>
@@ -4264,7 +4286,7 @@
         <v>5</v>
       </c>
       <c r="J178" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5234362050838021E-5</v>
       </c>
       <c r="K178" s="6">
@@ -4276,7 +4298,7 @@
         <v>1.5153511287030737E-4</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" ht="15.6">
       <c r="A179" t="s">
         <v>62</v>
       </c>
@@ -4300,7 +4322,7 @@
         <v>5</v>
       </c>
       <c r="J179" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.4186996206733058E-6</v>
       </c>
       <c r="K179" s="6">
@@ -4312,7 +4334,7 @@
         <v>5.9605695827406364E-6</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" ht="15.6">
       <c r="A180" t="s">
         <v>112</v>
       </c>
@@ -4336,7 +4358,7 @@
         <v>5</v>
       </c>
       <c r="J180" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.8519471687754242E-7</v>
       </c>
       <c r="K180" s="11">
@@ -4348,7 +4370,7 @@
         <v>3.1371418856529668E-7</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" ht="15.6">
       <c r="A182" s="1" t="s">
         <v>3</v>
       </c>
@@ -4356,7 +4378,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12">
       <c r="A183" t="s">
         <v>11</v>
       </c>
@@ -4364,7 +4386,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -4372,7 +4394,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12">
       <c r="A185" t="s">
         <v>4</v>
       </c>
@@ -4380,7 +4402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12">
       <c r="A186" t="s">
         <v>6</v>
       </c>
@@ -4388,7 +4410,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12">
       <c r="A187" t="s">
         <v>8</v>
       </c>
@@ -4396,7 +4418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12">
       <c r="A188" t="s">
         <v>91</v>
       </c>
@@ -4405,7 +4427,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12">
       <c r="A189" t="s">
         <v>92</v>
       </c>
@@ -4414,7 +4436,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12">
       <c r="A190" t="s">
         <v>93</v>
       </c>
@@ -4423,7 +4445,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12">
       <c r="A191" t="s">
         <v>153</v>
       </c>
@@ -4431,7 +4453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12">
       <c r="A192" t="s">
         <v>154</v>
       </c>
@@ -4439,7 +4461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12">
       <c r="A193" t="s">
         <v>155</v>
       </c>
@@ -4447,7 +4469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12">
       <c r="A194" t="s">
         <v>131</v>
       </c>
@@ -4456,7 +4478,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12">
       <c r="A195" t="s">
         <v>128</v>
       </c>
@@ -4465,7 +4487,7 @@
         <v>0.50434295320818157</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12">
       <c r="A196" t="s">
         <v>129</v>
       </c>
@@ -4474,7 +4496,7 @@
         <v>0.4539086578873634</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:12">
       <c r="A197" t="s">
         <v>130</v>
       </c>
@@ -4483,12 +4505,12 @@
         <v>0.55477724852899979</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" ht="15.6">
       <c r="A198" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12">
       <c r="A199" s="2" t="s">
         <v>13</v>
       </c>
@@ -4526,7 +4548,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12">
       <c r="A200" t="str">
         <f>B182</f>
         <v>transport, freight, sea, container ship, powered with diesel</v>
@@ -4549,7 +4571,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" ht="15.6">
       <c r="A201" t="s">
         <v>173</v>
       </c>
@@ -4588,7 +4610,7 @@
         <v>2.2390063070316696E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12">
       <c r="A202" t="s">
         <v>44</v>
       </c>
@@ -4615,7 +4637,7 @@
       <c r="K202" s="11"/>
       <c r="L202" s="11"/>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12">
       <c r="A203" t="s">
         <v>50</v>
       </c>
@@ -4642,7 +4664,7 @@
       <c r="K203" s="11"/>
       <c r="L203" s="11"/>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12">
       <c r="A204" t="s">
         <v>52</v>
       </c>
@@ -4666,7 +4688,7 @@
       <c r="K204" s="11"/>
       <c r="L204" s="11"/>
     </row>
-    <row r="205" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" ht="15.6">
       <c r="A205" t="s">
         <v>170</v>
       </c>
@@ -4702,7 +4724,7 @@
         <v>6.7170189210950092E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" ht="15.6">
       <c r="A206" t="s">
         <v>171</v>
       </c>
@@ -4726,7 +4748,7 @@
         <v>5</v>
       </c>
       <c r="J206" s="6">
-        <f t="shared" ref="J206" si="7">B206</f>
+        <f t="shared" ref="J206" si="8">B206</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K206" s="6">
@@ -4738,7 +4760,7 @@
         <v>1.2017798913043482E-5</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" ht="15.6">
       <c r="A207" t="s">
         <v>24</v>
       </c>
@@ -4762,7 +4784,7 @@
         <v>5</v>
       </c>
       <c r="J207" s="6">
-        <f t="shared" ref="J207:J211" si="8">B207</f>
+        <f t="shared" ref="J207:J211" si="9">B207</f>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K207" s="6">
@@ -4774,7 +4796,7 @@
         <v>3.4718085748792285E-5</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" ht="15.6">
       <c r="A208" t="s">
         <v>61</v>
       </c>
@@ -4798,7 +4820,7 @@
         <v>5</v>
       </c>
       <c r="J208" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K208" s="6">
@@ -4810,7 +4832,7 @@
         <v>6.5200000000000003E-6</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" ht="15.6">
       <c r="A209" t="s">
         <v>172</v>
       </c>
@@ -4834,7 +4856,7 @@
         <v>5</v>
       </c>
       <c r="J209" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K209" s="6">
@@ -4846,7 +4868,7 @@
         <v>1.3353109903381649E-7</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" ht="15.6">
       <c r="A210" t="s">
         <v>62</v>
       </c>
@@ -4870,7 +4892,7 @@
         <v>5</v>
       </c>
       <c r="J210" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K210" s="6">
@@ -4882,7 +4904,7 @@
         <v>5.3412439613526591E-6</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" ht="15.6">
       <c r="A211" t="s">
         <v>112</v>
       </c>
@@ -4906,7 +4928,7 @@
         <v>5</v>
       </c>
       <c r="J211" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K211" s="6">
@@ -4918,7 +4940,7 @@
         <v>4.0059329710144941E-7</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" ht="15.6">
       <c r="A213" s="1" t="s">
         <v>3</v>
       </c>
@@ -4926,7 +4948,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12">
       <c r="A214" t="s">
         <v>11</v>
       </c>
@@ -4934,7 +4956,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12">
       <c r="A215" t="s">
         <v>10</v>
       </c>
@@ -4942,7 +4964,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12">
       <c r="A216" t="s">
         <v>4</v>
       </c>
@@ -4950,7 +4972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12">
       <c r="A217" t="s">
         <v>6</v>
       </c>
@@ -4958,7 +4980,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12">
       <c r="A218" t="s">
         <v>8</v>
       </c>
@@ -4966,7 +4988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12">
       <c r="A219" t="s">
         <v>91</v>
       </c>
@@ -4975,7 +4997,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12">
       <c r="A220" t="s">
         <v>92</v>
       </c>
@@ -4984,7 +5006,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12">
       <c r="A221" t="s">
         <v>93</v>
       </c>
@@ -4993,7 +5015,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12">
       <c r="A222" t="s">
         <v>153</v>
       </c>
@@ -5002,7 +5024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12">
       <c r="A223" t="s">
         <v>154</v>
       </c>
@@ -5011,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12">
       <c r="A224" t="s">
         <v>155</v>
       </c>
@@ -5020,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:12">
       <c r="A225" t="s">
         <v>131</v>
       </c>
@@ -5029,7 +5051,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:12">
       <c r="A226" t="s">
         <v>128</v>
       </c>
@@ -5038,7 +5060,7 @@
         <v>0.50434295320818157</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:12">
       <c r="A227" t="s">
         <v>129</v>
       </c>
@@ -5047,7 +5069,7 @@
         <v>0.4539086578873634</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:12">
       <c r="A228" t="s">
         <v>130</v>
       </c>
@@ -5056,12 +5078,12 @@
         <v>0.55477724852899979</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" ht="15.6">
       <c r="A229" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:12">
       <c r="A230" s="2" t="s">
         <v>13</v>
       </c>
@@ -5099,7 +5121,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:12">
       <c r="A231" t="str">
         <f>B213</f>
         <v>transport, freight, sea, container ship, powered with synthetic diesel</v>
@@ -5122,7 +5144,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:12" ht="15.6">
       <c r="A232" t="s">
         <v>196</v>
       </c>
@@ -5161,7 +5183,7 @@
         <v>2.2390063070316696E-3</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:12">
       <c r="A233" t="s">
         <v>44</v>
       </c>
@@ -5188,7 +5210,7 @@
       <c r="K233" s="11"/>
       <c r="L233" s="11"/>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:12">
       <c r="A234" t="s">
         <v>50</v>
       </c>
@@ -5215,7 +5237,7 @@
       <c r="K234" s="11"/>
       <c r="L234" s="11"/>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:12">
       <c r="A235" t="s">
         <v>52</v>
       </c>
@@ -5239,7 +5261,7 @@
       <c r="K235" s="11"/>
       <c r="L235" s="11"/>
     </row>
-    <row r="236" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:12" ht="15.6">
       <c r="A236" t="s">
         <v>67</v>
       </c>
@@ -5275,7 +5297,7 @@
         <v>6.7170189210950092E-3</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" ht="15.6">
       <c r="A237" t="s">
         <v>60</v>
       </c>
@@ -5299,7 +5321,7 @@
         <v>5</v>
       </c>
       <c r="J237" s="6">
-        <f t="shared" ref="J237:J242" si="9">B237</f>
+        <f t="shared" ref="J237:J242" si="10">B237</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K237" s="6">
@@ -5311,7 +5333,7 @@
         <v>1.2017798913043482E-5</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:12" ht="15.6">
       <c r="A238" t="s">
         <v>24</v>
       </c>
@@ -5335,7 +5357,7 @@
         <v>5</v>
       </c>
       <c r="J238" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K238" s="6">
@@ -5347,7 +5369,7 @@
         <v>3.4718085748792285E-5</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:12" ht="15.6">
       <c r="A239" t="s">
         <v>61</v>
       </c>
@@ -5371,7 +5393,7 @@
         <v>5</v>
       </c>
       <c r="J239" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K239" s="6">
@@ -5383,7 +5405,7 @@
         <v>6.5200000000000003E-6</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:12" ht="15.6">
       <c r="A240" t="s">
         <v>111</v>
       </c>
@@ -5407,7 +5429,7 @@
         <v>5</v>
       </c>
       <c r="J240" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K240" s="6">
@@ -5419,7 +5441,7 @@
         <v>1.3353109903381649E-7</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:12" ht="15.6">
       <c r="A241" t="s">
         <v>62</v>
       </c>
@@ -5443,7 +5465,7 @@
         <v>5</v>
       </c>
       <c r="J241" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K241" s="6">
@@ -5455,7 +5477,7 @@
         <v>5.4747750603864751E-6</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:12" ht="15.6">
       <c r="A242" t="s">
         <v>112</v>
       </c>
@@ -5479,7 +5501,7 @@
         <v>5</v>
       </c>
       <c r="J242" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K242" s="6">
@@ -5491,7 +5513,7 @@
         <v>4.0059329710144941E-7</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:12" ht="15.6">
       <c r="A244" s="1" t="s">
         <v>3</v>
       </c>
@@ -5499,7 +5521,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:12">
       <c r="A245" t="s">
         <v>11</v>
       </c>
@@ -5507,7 +5529,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:12">
       <c r="A246" t="s">
         <v>10</v>
       </c>
@@ -5515,7 +5537,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:12">
       <c r="A247" t="s">
         <v>4</v>
       </c>
@@ -5523,7 +5545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -5531,7 +5553,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12">
       <c r="A249" t="s">
         <v>8</v>
       </c>
@@ -5539,7 +5561,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12">
       <c r="A250" t="s">
         <v>91</v>
       </c>
@@ -5548,7 +5570,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12">
       <c r="A251" t="s">
         <v>92</v>
       </c>
@@ -5557,7 +5579,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12">
       <c r="A252" t="s">
         <v>93</v>
       </c>
@@ -5566,7 +5588,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12">
       <c r="A253" t="s">
         <v>153</v>
       </c>
@@ -5575,7 +5597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12">
       <c r="A254" t="s">
         <v>154</v>
       </c>
@@ -5584,7 +5606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12">
       <c r="A255" t="s">
         <v>155</v>
       </c>
@@ -5593,7 +5615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12">
       <c r="A256" t="s">
         <v>131</v>
       </c>
@@ -5602,7 +5624,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:12">
       <c r="A257" t="s">
         <v>128</v>
       </c>
@@ -5611,7 +5633,7 @@
         <v>0.50434295320818157</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12">
       <c r="A258" t="s">
         <v>129</v>
       </c>
@@ -5620,7 +5642,7 @@
         <v>0.4539086578873634</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12">
       <c r="A259" t="s">
         <v>130</v>
       </c>
@@ -5629,12 +5651,12 @@
         <v>0.55477724852899979</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" ht="15.6">
       <c r="A260" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12">
       <c r="A261" s="2" t="s">
         <v>13</v>
       </c>
@@ -5672,7 +5694,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12">
       <c r="A262" t="str">
         <f>B244</f>
         <v>transport, freight, sea, container ship, powered with biodiesel</v>
@@ -5695,7 +5717,7 @@
         <v>transport, freight, sea, container ship</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" ht="15.6">
       <c r="A263" t="s">
         <v>168</v>
       </c>
@@ -5734,7 +5756,7 @@
         <v>2.2390063070316696E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12">
       <c r="A264" t="s">
         <v>44</v>
       </c>
@@ -5761,7 +5783,7 @@
       <c r="K264" s="11"/>
       <c r="L264" s="11"/>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12">
       <c r="A265" t="s">
         <v>50</v>
       </c>
@@ -5788,7 +5810,7 @@
       <c r="K265" s="11"/>
       <c r="L265" s="11"/>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12">
       <c r="A266" t="s">
         <v>52</v>
       </c>
@@ -5812,7 +5834,7 @@
       <c r="K266" s="11"/>
       <c r="L266" s="11"/>
     </row>
-    <row r="267" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" ht="15.6">
       <c r="A267" t="s">
         <v>67</v>
       </c>
@@ -5848,7 +5870,7 @@
         <v>6.7170189210950092E-3</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" ht="15.6">
       <c r="A268" t="s">
         <v>60</v>
       </c>
@@ -5872,7 +5894,7 @@
         <v>5</v>
       </c>
       <c r="J268" s="6">
-        <f t="shared" ref="J268:J273" si="10">B268</f>
+        <f t="shared" ref="J268:J273" si="11">B268</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K268" s="6">
@@ -5884,7 +5906,7 @@
         <v>1.2017798913043482E-5</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" ht="15.6">
       <c r="A269" t="s">
         <v>24</v>
       </c>
@@ -5908,7 +5930,7 @@
         <v>5</v>
       </c>
       <c r="J269" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K269" s="6">
@@ -5920,7 +5942,7 @@
         <v>3.4718085748792285E-5</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" ht="15.6">
       <c r="A270" t="s">
         <v>61</v>
       </c>
@@ -5944,7 +5966,7 @@
         <v>5</v>
       </c>
       <c r="J270" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K270" s="6">
@@ -5956,7 +5978,7 @@
         <v>6.5200000000000003E-6</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" ht="15.6">
       <c r="A271" t="s">
         <v>111</v>
       </c>
@@ -5980,7 +6002,7 @@
         <v>5</v>
       </c>
       <c r="J271" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K271" s="6">
@@ -5992,7 +6014,7 @@
         <v>1.3353109903381649E-7</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" ht="15.6">
       <c r="A272" t="s">
         <v>62</v>
       </c>
@@ -6016,7 +6038,7 @@
         <v>5</v>
       </c>
       <c r="J272" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K272" s="6">
@@ -6028,7 +6050,7 @@
         <v>5.4747750603864751E-6</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" ht="15.6">
       <c r="A273" t="s">
         <v>112</v>
       </c>
@@ -6052,7 +6074,7 @@
         <v>5</v>
       </c>
       <c r="J273" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K273" s="6">
@@ -6074,32 +6096,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F1A7F4-A2B5-7747-AA61-2990069064F9}">
   <dimension ref="A1:P24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.5" customWidth="1"/>
-    <col min="9" max="9" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.44140625" customWidth="1"/>
+    <col min="9" max="9" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="B3" s="2" t="s">
         <v>76</v>
       </c>
@@ -6146,7 +6168,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="B4" t="s">
         <v>163</v>
       </c>
@@ -6193,7 +6215,7 @@
         <v>180000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="B5" t="s">
         <v>80</v>
       </c>
@@ -6247,7 +6269,7 @@
         <v>153000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="B6" t="s">
         <v>82</v>
       </c>
@@ -6301,7 +6323,7 @@
         <v>153000000000</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="B7" t="s">
         <v>84</v>
       </c>
@@ -6355,7 +6377,7 @@
         <v>135000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="B8" t="s">
         <v>86</v>
       </c>
@@ -6409,7 +6431,7 @@
         <v>108000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="B9" t="s">
         <v>101</v>
       </c>
@@ -6462,7 +6484,7 @@
         <v>162000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="B10" t="s">
         <v>99</v>
       </c>
@@ -6515,7 +6537,7 @@
         <v>117000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="B11" t="s">
         <v>193</v>
       </c>
@@ -6572,10 +6594,10 @@
         <v>166602577214.15421</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="O12" s="11"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="B14" s="2" t="s">
         <v>124</v>
       </c>
@@ -6589,7 +6611,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="B15" t="s">
         <v>177</v>
       </c>
@@ -6604,7 +6626,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="B16" t="s">
         <v>80</v>
       </c>
@@ -6621,7 +6643,7 @@
         <v>0.54620930740659834</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:5">
       <c r="B17" t="s">
         <v>82</v>
       </c>
@@ -6636,7 +6658,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:5">
       <c r="B18" t="s">
         <v>84</v>
       </c>
@@ -6651,7 +6673,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:5">
       <c r="B19" t="s">
         <v>86</v>
       </c>
@@ -6666,7 +6688,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
         <v>101</v>
       </c>
@@ -6683,7 +6705,7 @@
         <v>0.54276315789473695</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:5">
       <c r="B21" t="s">
         <v>99</v>
       </c>
@@ -6700,7 +6722,7 @@
         <v>0.54276315789473695</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:5">
       <c r="B22" t="s">
         <v>178</v>
       </c>
@@ -6717,7 +6739,7 @@
         <v>0.55477724852899979</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:5">
       <c r="B23" t="s">
         <v>193</v>
       </c>
@@ -6734,7 +6756,7 @@
         <v>0.54276315789473695</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:5">
       <c r="B24" t="s">
         <v>179</v>
       </c>

--- a/premise/data/additional_inventories/lci-ships.xlsx
+++ b/premise/data/additional_inventories/lci-ships.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ac145674\coding_projects\premise_h2-distribution\premise\data\additional_inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA23D2A4-BEA8-4936-BBFE-826CDCD39D6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B79077-8F25-4DC2-B2E2-0B7C8F7DAEBC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10500" yWindow="660" windowWidth="25824" windowHeight="18984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2490,8 +2490,8 @@
         <v>4.5451388888888888E-8</v>
       </c>
       <c r="K84" s="6">
-        <f t="shared" ref="K84:K86" si="2">0.00002*(B77*18.6*B72/3.6)</f>
-        <v>1.6145833333333334E-12</v>
+        <f>0.00002*(B76*18.6*B71/3.6)</f>
+        <v>2.5812601273148154E-7</v>
       </c>
       <c r="L84" s="6">
         <f>0.0000028*(B76*18.6*B72/3.6)</f>
@@ -2526,8 +2526,8 @@
         <v>6.4930555555555568E-7</v>
       </c>
       <c r="K85" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>0.00002*(B76*18.6*B71/3.6)</f>
+        <v>2.5812601273148154E-7</v>
       </c>
       <c r="L85" s="6">
         <f>0.00004*(B76*18.6*B72/3.6)</f>
@@ -2561,9 +2561,9 @@
         <f t="shared" si="1"/>
         <v>7.4670138888888891E-7</v>
       </c>
-      <c r="K86" s="6" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+      <c r="K86" s="6">
+        <f>0.00002*(B76*18.6*B71/3.6)</f>
+        <v>2.5812601273148154E-7</v>
       </c>
       <c r="L86">
         <f>0.00013*(B76*18.6*B72/3.6)</f>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="J112" s="6">
-        <f t="shared" ref="J112:J115" si="3">B112</f>
+        <f t="shared" ref="J112:J115" si="2">B112</f>
         <v>7.7916666666666672E-5</v>
       </c>
       <c r="K112" s="6">
@@ -3015,7 +3015,7 @@
         <v>5</v>
       </c>
       <c r="J113" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>9.3613953124999986E-5</v>
       </c>
       <c r="K113" s="6">
@@ -3051,7 +3051,7 @@
         <v>5</v>
       </c>
       <c r="J114" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4.2035554687499993E-5</v>
       </c>
       <c r="K114" s="6">
@@ -3087,7 +3087,7 @@
         <v>5</v>
       </c>
       <c r="J115" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7.953993055555555E-9</v>
       </c>
       <c r="K115" s="6">
@@ -3509,7 +3509,7 @@
         <v>5</v>
       </c>
       <c r="J141" s="6">
-        <f t="shared" ref="J141:J144" si="4">B141</f>
+        <f t="shared" ref="J141:J144" si="3">B141</f>
         <v>4.0680701754385975E-5</v>
       </c>
       <c r="K141" s="6">
@@ -3545,7 +3545,7 @@
         <v>5</v>
       </c>
       <c r="J142" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.5589473684210534E-5</v>
       </c>
       <c r="K142" s="6">
@@ -3581,7 +3581,7 @@
         <v>5</v>
       </c>
       <c r="J143" s="6">
-        <f t="shared" ref="J143" si="5">B143</f>
+        <f t="shared" ref="J143" si="4">B143</f>
         <v>6.5614035087719314E-7</v>
       </c>
       <c r="K143" s="6">
@@ -3617,7 +3617,7 @@
         <v>5</v>
       </c>
       <c r="J144" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.5614035087719314E-7</v>
       </c>
       <c r="K144" s="6">
@@ -3653,7 +3653,7 @@
         <v>5</v>
       </c>
       <c r="J145" s="6">
-        <f t="shared" ref="J145:J147" si="6">B145</f>
+        <f t="shared" ref="J145:J147" si="5">B145</f>
         <v>6.6488888888888891E-5</v>
       </c>
       <c r="K145" s="6">
@@ -3689,7 +3689,7 @@
         <v>5</v>
       </c>
       <c r="J146" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.311111111111113E-6</v>
       </c>
       <c r="K146" s="6">
@@ -3725,7 +3725,7 @@
         <v>5</v>
       </c>
       <c r="J147" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.3742690058479546E-7</v>
       </c>
       <c r="K147" s="11">
@@ -4142,7 +4142,7 @@
         <v>5</v>
       </c>
       <c r="J174" s="6">
-        <f t="shared" ref="J174:J180" si="7">B174</f>
+        <f t="shared" ref="J174:J180" si="6">B174</f>
         <v>2.6523108669611446E-5</v>
       </c>
       <c r="K174" s="6">
@@ -4178,7 +4178,7 @@
         <v>5</v>
       </c>
       <c r="J175" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.6683890937336232E-5</v>
       </c>
       <c r="K175" s="6">
@@ -4214,7 +4214,7 @@
         <v>5</v>
       </c>
       <c r="J176" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4.2779207531631361E-7</v>
       </c>
       <c r="K176" s="6">
@@ -4250,7 +4250,7 @@
         <v>5</v>
       </c>
       <c r="J177" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4.2779207531631361E-7</v>
       </c>
       <c r="K177" s="6">
@@ -4286,7 +4286,7 @@
         <v>5</v>
       </c>
       <c r="J178" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4.5234362050838021E-5</v>
       </c>
       <c r="K178" s="6">
@@ -4322,7 +4322,7 @@
         <v>5</v>
       </c>
       <c r="J179" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5.4186996206733058E-6</v>
       </c>
       <c r="K179" s="6">
@@ -4358,7 +4358,7 @@
         <v>5</v>
       </c>
       <c r="J180" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.8519471687754242E-7</v>
       </c>
       <c r="K180" s="11">
@@ -4748,7 +4748,7 @@
         <v>5</v>
       </c>
       <c r="J206" s="6">
-        <f t="shared" ref="J206" si="8">B206</f>
+        <f t="shared" ref="J206" si="7">B206</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K206" s="6">
@@ -4784,7 +4784,7 @@
         <v>5</v>
       </c>
       <c r="J207" s="6">
-        <f t="shared" ref="J207:J211" si="9">B207</f>
+        <f t="shared" ref="J207:J211" si="8">B207</f>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K207" s="6">
@@ -4820,7 +4820,7 @@
         <v>5</v>
       </c>
       <c r="J208" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K208" s="6">
@@ -4856,7 +4856,7 @@
         <v>5</v>
       </c>
       <c r="J209" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K209" s="6">
@@ -4892,7 +4892,7 @@
         <v>5</v>
       </c>
       <c r="J210" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K210" s="6">
@@ -4928,7 +4928,7 @@
         <v>5</v>
       </c>
       <c r="J211" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K211" s="6">
@@ -5321,7 +5321,7 @@
         <v>5</v>
       </c>
       <c r="J237" s="6">
-        <f t="shared" ref="J237:J242" si="10">B237</f>
+        <f t="shared" ref="J237:J242" si="9">B237</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K237" s="6">
@@ -5357,7 +5357,7 @@
         <v>5</v>
       </c>
       <c r="J238" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K238" s="6">
@@ -5393,7 +5393,7 @@
         <v>5</v>
       </c>
       <c r="J239" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K239" s="6">
@@ -5429,7 +5429,7 @@
         <v>5</v>
       </c>
       <c r="J240" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K240" s="6">
@@ -5465,7 +5465,7 @@
         <v>5</v>
       </c>
       <c r="J241" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K241" s="6">
@@ -5501,7 +5501,7 @@
         <v>5</v>
       </c>
       <c r="J242" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K242" s="6">
@@ -5894,7 +5894,7 @@
         <v>5</v>
       </c>
       <c r="J268" s="6">
-        <f t="shared" ref="J268:J273" si="11">B268</f>
+        <f t="shared" ref="J268:J273" si="10">B268</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K268" s="6">
@@ -5930,7 +5930,7 @@
         <v>5</v>
       </c>
       <c r="J269" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K269" s="6">
@@ -5966,7 +5966,7 @@
         <v>5</v>
       </c>
       <c r="J270" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K270" s="6">
@@ -6002,7 +6002,7 @@
         <v>5</v>
       </c>
       <c r="J271" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K271" s="6">
@@ -6038,7 +6038,7 @@
         <v>5</v>
       </c>
       <c r="J272" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K272" s="6">
@@ -6074,7 +6074,7 @@
         <v>5</v>
       </c>
       <c r="J273" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K273" s="6">

--- a/premise/data/additional_inventories/lci-ships.xlsx
+++ b/premise/data/additional_inventories/lci-ships.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ac145674\coding_projects\premise_h2-distribution\premise\data\additional_inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B79077-8F25-4DC2-B2E2-0B7C8F7DAEBC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3330479E-78EE-47B5-B16F-79D238DE7AC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10500" yWindow="660" windowWidth="25824" windowHeight="18984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8652" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inventories" sheetId="1" r:id="rId1"/>
-    <sheet name="parameters" sheetId="2" r:id="rId2"/>
+    <sheet name="Tabelle1" sheetId="3" r:id="rId2"/>
+    <sheet name="parameters" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">inventories!$A$1:$O$225</definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="200">
   <si>
     <t>Database</t>
   </si>
@@ -1325,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" ref="J23:J28" si="0">B23</f>
+        <f>B23</f>
         <v>1.2150747238466536E-3</v>
       </c>
       <c r="K23" s="6">
@@ -1366,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="J24" s="11">
-        <f t="shared" si="0"/>
+        <f>B24</f>
         <v>1.316872427983539E-8</v>
       </c>
       <c r="K24" s="9">
@@ -1405,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="J25" s="11">
-        <f t="shared" si="0"/>
+        <f>B25</f>
         <v>1.6543209876543209E-6</v>
       </c>
       <c r="K25" s="9">
@@ -1444,7 +1445,7 @@
         <v>5</v>
       </c>
       <c r="J26" s="11">
-        <f t="shared" si="0"/>
+        <f>B26</f>
         <v>5.5144032921810691E-6</v>
       </c>
       <c r="K26" s="9">
@@ -1483,7 +1484,7 @@
         <v>5</v>
       </c>
       <c r="J27" s="11">
-        <f t="shared" si="0"/>
+        <f>B27</f>
         <v>8.2304526748971185E-12</v>
       </c>
       <c r="K27" s="11">
@@ -1522,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="J28" s="11">
-        <f t="shared" si="0"/>
+        <f>B28</f>
         <v>8.2304526748971185E-12</v>
       </c>
       <c r="K28" s="11">
@@ -2378,7 +2379,7 @@
         <v>5</v>
       </c>
       <c r="J81" s="6">
-        <f t="shared" ref="J81:J86" si="1">B81</f>
+        <f>B81</f>
         <v>2.1102430555555555E-6</v>
       </c>
       <c r="K81" s="6">
@@ -2414,7 +2415,7 @@
         <v>5</v>
       </c>
       <c r="J82" s="6">
-        <f t="shared" si="1"/>
+        <f>B82</f>
         <v>4.2204861111111112E-5</v>
       </c>
       <c r="K82" s="6">
@@ -2450,7 +2451,7 @@
         <v>5</v>
       </c>
       <c r="J83" s="6">
-        <f t="shared" si="1"/>
+        <f>B83</f>
         <v>3.2465277777777784E-7</v>
       </c>
       <c r="K83" s="6">
@@ -2467,7 +2468,7 @@
         <v>62</v>
       </c>
       <c r="B84">
-        <f>0.0000028*(B76*18.6*B70/3.6)</f>
+        <f>0.0000028*(inventories!B76*18.6*inventories!B70/3.6)</f>
         <v>4.5451388888888888E-8</v>
       </c>
       <c r="D84" t="s">
@@ -2486,15 +2487,15 @@
         <v>5</v>
       </c>
       <c r="J84" s="6">
-        <f t="shared" si="1"/>
+        <f>B84</f>
         <v>4.5451388888888888E-8</v>
       </c>
       <c r="K84" s="6">
-        <f>0.00002*(B76*18.6*B71/3.6)</f>
-        <v>2.5812601273148154E-7</v>
+        <f>0.0000028*(inventories!B76*18.6*inventories!B71/3.6)</f>
+        <v>3.6137641782407408E-8</v>
       </c>
       <c r="L84" s="6">
-        <f>0.0000028*(B76*18.6*B72/3.6)</f>
+        <f>0.0000028*(inventories!B76*18.6*inventories!B72/3.6)</f>
         <v>4.6462682291666672E-8</v>
       </c>
     </row>
@@ -2522,12 +2523,12 @@
         <v>5</v>
       </c>
       <c r="J85" s="6">
-        <f t="shared" si="1"/>
+        <f>B85</f>
         <v>6.4930555555555568E-7</v>
       </c>
       <c r="K85" s="6">
-        <f>0.00002*(B76*18.6*B71/3.6)</f>
-        <v>2.5812601273148154E-7</v>
+        <f>0.00004*(B76*18.6*B71/3.6)</f>
+        <v>5.1625202546296308E-7</v>
       </c>
       <c r="L85" s="6">
         <f>0.00004*(B76*18.6*B72/3.6)</f>
@@ -2558,12 +2559,12 @@
         <v>5</v>
       </c>
       <c r="J86" s="6">
-        <f t="shared" si="1"/>
+        <f>B86</f>
         <v>7.4670138888888891E-7</v>
       </c>
-      <c r="K86" s="6">
-        <f>0.00002*(B76*18.6*B71/3.6)</f>
-        <v>2.5812601273148154E-7</v>
+      <c r="K86" s="11">
+        <f>0.00001*(B76*18.6*B71/3.6)</f>
+        <v>1.2906300636574077E-7</v>
       </c>
       <c r="L86">
         <f>0.00013*(B76*18.6*B72/3.6)</f>
@@ -2979,7 +2980,7 @@
         <v>5</v>
       </c>
       <c r="J112" s="6">
-        <f t="shared" ref="J112:J115" si="2">B112</f>
+        <f t="shared" ref="J112:J115" si="0">B112</f>
         <v>7.7916666666666672E-5</v>
       </c>
       <c r="K112" s="6">
@@ -3015,7 +3016,7 @@
         <v>5</v>
       </c>
       <c r="J113" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>9.3613953124999986E-5</v>
       </c>
       <c r="K113" s="6">
@@ -3051,7 +3052,7 @@
         <v>5</v>
       </c>
       <c r="J114" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.2035554687499993E-5</v>
       </c>
       <c r="K114" s="6">
@@ -3087,7 +3088,7 @@
         <v>5</v>
       </c>
       <c r="J115" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7.953993055555555E-9</v>
       </c>
       <c r="K115" s="6">
@@ -3509,7 +3510,7 @@
         <v>5</v>
       </c>
       <c r="J141" s="6">
-        <f t="shared" ref="J141:J144" si="3">B141</f>
+        <f t="shared" ref="J141:J144" si="1">B141</f>
         <v>4.0680701754385975E-5</v>
       </c>
       <c r="K141" s="6">
@@ -3545,7 +3546,7 @@
         <v>5</v>
       </c>
       <c r="J142" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2.5589473684210534E-5</v>
       </c>
       <c r="K142" s="6">
@@ -3581,7 +3582,7 @@
         <v>5</v>
       </c>
       <c r="J143" s="6">
-        <f t="shared" ref="J143" si="4">B143</f>
+        <f t="shared" ref="J143" si="2">B143</f>
         <v>6.5614035087719314E-7</v>
       </c>
       <c r="K143" s="6">
@@ -3617,7 +3618,7 @@
         <v>5</v>
       </c>
       <c r="J144" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6.5614035087719314E-7</v>
       </c>
       <c r="K144" s="6">
@@ -3653,7 +3654,7 @@
         <v>5</v>
       </c>
       <c r="J145" s="6">
-        <f t="shared" ref="J145:J147" si="5">B145</f>
+        <f t="shared" ref="J145:J147" si="3">B145</f>
         <v>6.6488888888888891E-5</v>
       </c>
       <c r="K145" s="6">
@@ -3689,7 +3690,7 @@
         <v>5</v>
       </c>
       <c r="J146" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>8.311111111111113E-6</v>
       </c>
       <c r="K146" s="6">
@@ -3725,7 +3726,7 @@
         <v>5</v>
       </c>
       <c r="J147" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>4.3742690058479546E-7</v>
       </c>
       <c r="K147" s="11">
@@ -4142,7 +4143,7 @@
         <v>5</v>
       </c>
       <c r="J174" s="6">
-        <f t="shared" ref="J174:J180" si="6">B174</f>
+        <f t="shared" ref="J174:J180" si="4">B174</f>
         <v>2.6523108669611446E-5</v>
       </c>
       <c r="K174" s="6">
@@ -4178,7 +4179,7 @@
         <v>5</v>
       </c>
       <c r="J175" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1.6683890937336232E-5</v>
       </c>
       <c r="K175" s="6">
@@ -4214,7 +4215,7 @@
         <v>5</v>
       </c>
       <c r="J176" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4.2779207531631361E-7</v>
       </c>
       <c r="K176" s="6">
@@ -4250,7 +4251,7 @@
         <v>5</v>
       </c>
       <c r="J177" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4.2779207531631361E-7</v>
       </c>
       <c r="K177" s="6">
@@ -4286,7 +4287,7 @@
         <v>5</v>
       </c>
       <c r="J178" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4.5234362050838021E-5</v>
       </c>
       <c r="K178" s="6">
@@ -4322,7 +4323,7 @@
         <v>5</v>
       </c>
       <c r="J179" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5.4186996206733058E-6</v>
       </c>
       <c r="K179" s="6">
@@ -4358,7 +4359,7 @@
         <v>5</v>
       </c>
       <c r="J180" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2.8519471687754242E-7</v>
       </c>
       <c r="K180" s="11">
@@ -4748,7 +4749,7 @@
         <v>5</v>
       </c>
       <c r="J206" s="6">
-        <f t="shared" ref="J206" si="7">B206</f>
+        <f t="shared" ref="J206" si="5">B206</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K206" s="6">
@@ -4784,7 +4785,7 @@
         <v>5</v>
       </c>
       <c r="J207" s="6">
-        <f t="shared" ref="J207:J211" si="8">B207</f>
+        <f t="shared" ref="J207:J211" si="6">B207</f>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K207" s="6">
@@ -4820,7 +4821,7 @@
         <v>5</v>
       </c>
       <c r="J208" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K208" s="6">
@@ -4856,7 +4857,7 @@
         <v>5</v>
       </c>
       <c r="J209" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K209" s="6">
@@ -4892,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="J210" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K210" s="6">
@@ -4928,7 +4929,7 @@
         <v>5</v>
       </c>
       <c r="J211" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K211" s="6">
@@ -5321,7 +5322,7 @@
         <v>5</v>
       </c>
       <c r="J237" s="6">
-        <f t="shared" ref="J237:J242" si="9">B237</f>
+        <f t="shared" ref="J237:J242" si="7">B237</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K237" s="6">
@@ -5357,7 +5358,7 @@
         <v>5</v>
       </c>
       <c r="J238" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K238" s="6">
@@ -5393,7 +5394,7 @@
         <v>5</v>
       </c>
       <c r="J239" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K239" s="6">
@@ -5429,7 +5430,7 @@
         <v>5</v>
       </c>
       <c r="J240" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K240" s="6">
@@ -5465,7 +5466,7 @@
         <v>5</v>
       </c>
       <c r="J241" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K241" s="6">
@@ -5501,7 +5502,7 @@
         <v>5</v>
       </c>
       <c r="J242" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K242" s="6">
@@ -5894,7 +5895,7 @@
         <v>5</v>
       </c>
       <c r="J268" s="6">
-        <f t="shared" ref="J268:J273" si="10">B268</f>
+        <f t="shared" ref="J268:J273" si="8">B268</f>
         <v>1.0925271739130437E-5</v>
       </c>
       <c r="K268" s="6">
@@ -5930,7 +5931,7 @@
         <v>5</v>
       </c>
       <c r="J269" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3.1561896135265709E-5</v>
       </c>
       <c r="K269" s="6">
@@ -5966,7 +5967,7 @@
         <v>5</v>
       </c>
       <c r="J270" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3.2600000000000001E-6</v>
       </c>
       <c r="K270" s="6">
@@ -6002,7 +6003,7 @@
         <v>5</v>
       </c>
       <c r="J271" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1.2139190821256042E-7</v>
       </c>
       <c r="K271" s="6">
@@ -6038,7 +6039,7 @@
         <v>5</v>
       </c>
       <c r="J272" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>4.9770682367149768E-6</v>
       </c>
       <c r="K272" s="6">
@@ -6074,7 +6075,7 @@
         <v>5</v>
       </c>
       <c r="J273" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3.6417572463768126E-7</v>
       </c>
       <c r="K273" s="6">
@@ -6094,6 +6095,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCE0B57-8EBF-4406-A9BA-F0BE72B7B07B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F1A7F4-A2B5-7747-AA61-2990069064F9}">
   <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
